--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_37.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3688712.991279981</v>
+        <v>3728718.243907453</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6730379.30184654</v>
+        <v>6730379.301846541</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6730379.30184654</v>
+        <v>6730379.301846541</v>
       </c>
     </row>
     <row r="9">
@@ -666,7 +666,7 @@
         <v>4.363289606868648</v>
       </c>
       <c r="F2" t="n">
-        <v>404.8896287080119</v>
+        <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
         <v>403.7573722870162</v>
@@ -705,10 +705,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>94.84816780232291</v>
+        <v>230.1466006767582</v>
       </c>
       <c r="T2" t="n">
-        <v>321.9740146029993</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>67.51997340159467</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -778,10 +778,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>403.3164791381267</v>
       </c>
       <c r="S3" t="n">
         <v>66.5639999646113</v>
@@ -790,7 +790,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -900,16 +900,16 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E5" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F5" t="n">
         <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H5" t="n">
-        <v>143.3080915779632</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -942,10 +942,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>94.84816780232291</v>
+        <v>494.8481678023229</v>
       </c>
       <c r="T5" t="n">
-        <v>586.6755817285639</v>
+        <v>321.9740146029993</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -982,10 +982,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,16 +1015,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
-        <v>147.2737972923793</v>
+        <v>166.5443783724179</v>
       </c>
       <c r="S6" t="n">
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>405.3577652175138</v>
+        <v>5.357765217513816</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1033,10 +1033,10 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>77.5883638288102</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1128,7 +1128,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>217.2977458300097</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
         <v>49.47457824299391</v>
@@ -1149,7 +1149,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>136.2581913854141</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1176,25 +1176,25 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>494.8481678023229</v>
       </c>
       <c r="T8" t="n">
-        <v>186.6755817285639</v>
+        <v>586.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V8" t="n">
-        <v>229.8510241668239</v>
+        <v>629.8510241668239</v>
       </c>
       <c r="W8" t="n">
         <v>238.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>592.2818334606677</v>
+        <v>192.2818334606677</v>
       </c>
       <c r="Y8" t="n">
         <v>111.3174326828064</v>
@@ -1210,19 +1210,19 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>57.72562438342266</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>189.3139912864826</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U9" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
       </c>
       <c r="W9" t="n">
-        <v>432.3731429098285</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X9" t="n">
         <v>19.86273944538755</v>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
         <v>179.3632896068686</v>
@@ -1413,16 +1413,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
         <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>46.27647083429436</v>
       </c>
       <c r="V11" t="n">
         <v>404.8510241668239</v>
@@ -1434,7 +1434,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.91409276364498</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>9.281668720333455</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>49.38285596774193</v>
       </c>
       <c r="G13" t="n">
         <v>20.04387284153003</v>
@@ -1550,10 +1550,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1562,7 +1562,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>121.0311678260091</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1586,10 +1586,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>132.0096587035274</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.2581913854141848</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>218.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>310.9337731139786</v>
+        <v>310.6755817285639</v>
       </c>
       <c r="U14" t="n">
         <v>373.2212965486107</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>12.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -1802,16 +1802,16 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>304.0583293563777</v>
       </c>
       <c r="Q16" t="n">
-        <v>204.4012142968261</v>
+        <v>449.839266425598</v>
       </c>
       <c r="R16" t="n">
-        <v>450.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>86.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1860,7 +1860,7 @@
         <v>132.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2581913854141848</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>310.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>373.2212965486107</v>
+        <v>373.4794879340254</v>
       </c>
       <c r="V17" t="n">
         <v>353.8510241668239</v>
@@ -2003,7 +2003,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -2036,19 +2036,19 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>364.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>293.5423339445498</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>449.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>304.0583293563777</v>
       </c>
       <c r="S19" t="n">
-        <v>86.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2097,7 +2097,7 @@
         <v>132.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>0.2581913854141848</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,7 +2124,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2581913854146068</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>218.8481678023229</v>
@@ -2261,25 +2261,25 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>12.52077380114304</v>
       </c>
       <c r="L22" t="n">
         <v>147.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>244.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>295.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>54.01250714881864</v>
       </c>
       <c r="P22" t="n">
-        <v>156.5107011985985</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>449.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2319,7 +2319,7 @@
         <v>173.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>134.3391557398498</v>
+        <v>134.597347125264</v>
       </c>
       <c r="E23" t="n">
         <v>128.3632896068686</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2581913854146068</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
         <v>218.8481678023229</v>
@@ -2471,16 +2471,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>11.11380033707866</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>9.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>4.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2504,25 +2504,25 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>47.26462318201327</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>295.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>411.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>179.8257120189161</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>450.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>86.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>11.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -2550,25 +2550,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>207.4229050358148</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C26" t="n">
-        <v>224.4745782429939</v>
+        <v>212.696475845388</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>361.6755817285639</v>
@@ -2613,7 +2613,7 @@
         <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>413.3734759809475</v>
       </c>
       <c r="X26" t="n">
         <v>367.2818334606677</v>
@@ -2738,7 +2738,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>142.2291713307484</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>0</v>
@@ -2756,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>340.7767994885276</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2814,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>62.12488247690044</v>
       </c>
       <c r="L29" t="n">
-        <v>616.9388964877596</v>
+        <v>554.8140140108974</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2978,7 +2978,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>231.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
         <v>0</v>
@@ -2987,16 +2987,16 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>398.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>279.0492164635681</v>
+        <v>398.1531175103889</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>437.6021279811511</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>73.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3045,16 +3045,16 @@
         <v>119.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>3.741391385414349</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>62.12488247690068</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>554.814014010788</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>616.9388964877817</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3081,7 +3081,7 @@
         <v>297.6755817285639</v>
       </c>
       <c r="U32" t="n">
-        <v>360.2212965486107</v>
+        <v>363.9626879340252</v>
       </c>
       <c r="V32" t="n">
         <v>340.8510241668239</v>
@@ -3212,28 +3212,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>134.5476281577792</v>
       </c>
       <c r="M34" t="n">
         <v>231.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>282.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>167.2843676633921</v>
+        <v>260.7644103623815</v>
       </c>
       <c r="P34" t="n">
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>436.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
       <c r="S34" t="n">
-        <v>73.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -3288,13 +3288,13 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>62.12488247690055</v>
+        <v>62.12488247690023</v>
       </c>
       <c r="L35" t="n">
-        <v>554.8140140109142</v>
+        <v>372.538008032207</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>182.2760059785674</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -3455,22 +3455,22 @@
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>282.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>34.68733078764637</v>
       </c>
       <c r="Q37" t="n">
         <v>436.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>116.7309037942571</v>
+        <v>437.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>73.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>115.3632896068686</v>
       </c>
       <c r="F38" t="n">
-        <v>115.8896287080119</v>
+        <v>119.6310200934262</v>
       </c>
       <c r="G38" t="n">
         <v>114.7573722870162</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>62.12488247690062</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>554.8140140109156</v>
+        <v>616.9388964877652</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3564,7 +3564,7 @@
         <v>349.3734759809475</v>
       </c>
       <c r="X38" t="n">
-        <v>307.0232248460821</v>
+        <v>303.2818334606677</v>
       </c>
       <c r="Y38" t="n">
         <v>222.3174326828064</v>
@@ -3686,28 +3686,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>134.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>20.57464473379835</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>282.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>351.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>120.0810331342294</v>
+        <v>398.4478973282775</v>
       </c>
       <c r="Q40" t="n">
         <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>437.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>73.37347970285543</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -3738,13 +3738,13 @@
         <v>303.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>271.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>232.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>226.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>226.8896287080119</v>
@@ -3783,16 +3783,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>72.87859882829446</v>
+        <v>11.49895253293992</v>
       </c>
       <c r="S41" t="n">
         <v>316.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>379.5187584665654</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>471.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -3801,7 +3801,7 @@
         <v>460.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>414.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>333.3174326828064</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>206.5565566463266</v>
       </c>
       <c r="C42" t="n">
         <v>183.0999124455193</v>
@@ -3823,13 +3823,13 @@
         <v>169.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>164.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>161.6362423378769</v>
       </c>
       <c r="G42" t="n">
-        <v>147.7395358750273</v>
+        <v>45.3565096303668</v>
       </c>
       <c r="H42" t="n">
         <v>154.1680871864211</v>
@@ -3862,22 +3862,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>369.2737972923793</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>288.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>227.3577652175138</v>
       </c>
       <c r="U42" t="n">
         <v>222.2103597601867</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>236.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>31.24084739968526</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
         <v>241.8627394453875</v>
@@ -3893,7 +3893,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>109.1138003370787</v>
+        <v>0</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
@@ -3947,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>32.02456650625771</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3975,16 +3975,16 @@
         <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>386.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>341.3632896068686</v>
+        <v>164.1074061900851</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>341.8896287080119</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -3993,7 +3993,7 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>87.08115968268461</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4020,13 +4020,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>187.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>523.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>586.2212965486107</v>
@@ -4035,10 +4035,10 @@
         <v>566.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>281.7548167553475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>529.2818334606677</v>
       </c>
       <c r="Y44" t="n">
         <v>448.3174326828064</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>321.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>298.0999124455193</v>
@@ -4060,19 +4060,19 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>279.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>262.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>269.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>154.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>110.0792650904796</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -4108,19 +4108,19 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>37.09438864780449</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>351.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>278.0311757283962</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>336.3913927661343</v>
       </c>
     </row>
     <row r="46">
@@ -4297,16 +4297,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1511.368528253487</v>
+        <v>1107.328124213083</v>
       </c>
       <c r="C2" t="n">
-        <v>1461.394206795918</v>
+        <v>1057.353802755514</v>
       </c>
       <c r="D2" t="n">
-        <v>1450.950615139504</v>
+        <v>1046.9102110991</v>
       </c>
       <c r="E2" t="n">
-        <v>1446.543251900242</v>
+        <v>1042.502847859839</v>
       </c>
       <c r="F2" t="n">
         <v>1037.563828962857</v>
@@ -4324,19 +4324,19 @@
         <v>457.3091130376557</v>
       </c>
       <c r="K2" t="n">
-        <v>614.6805851725693</v>
+        <v>1167.015479385524</v>
       </c>
       <c r="L2" t="n">
-        <v>614.6805851725693</v>
+        <v>1167.015479385524</v>
       </c>
       <c r="M2" t="n">
-        <v>614.6805851725693</v>
+        <v>1431.430585172569</v>
       </c>
       <c r="N2" t="n">
-        <v>1227.900904947332</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="O2" t="n">
-        <v>2044.650904947332</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="P2" t="n">
         <v>2861.400904947332</v>
@@ -4348,25 +4348,25 @@
         <v>3046.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2950.781043807457</v>
+        <v>2814.115960095906</v>
       </c>
       <c r="T2" t="n">
-        <v>2625.55476643069</v>
+        <v>2221.514362390286</v>
       </c>
       <c r="U2" t="n">
-        <v>2373.816083048255</v>
+        <v>1969.775679007851</v>
       </c>
       <c r="V2" t="n">
-        <v>2141.643331364595</v>
+        <v>1737.602927324191</v>
       </c>
       <c r="W2" t="n">
-        <v>1900.862042494951</v>
+        <v>1496.821638454547</v>
       </c>
       <c r="X2" t="n">
-        <v>1706.637968292256</v>
+        <v>1302.597564251852</v>
       </c>
       <c r="Y2" t="n">
-        <v>1594.196117097502</v>
+        <v>1190.155713057098</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>353.521575043377</v>
+        <v>285.3195817084329</v>
       </c>
       <c r="C3" t="n">
-        <v>353.521575043377</v>
+        <v>285.3195817084329</v>
       </c>
       <c r="D3" t="n">
-        <v>353.521575043377</v>
+        <v>285.3195817084329</v>
       </c>
       <c r="E3" t="n">
-        <v>353.521575043377</v>
+        <v>285.3195817084329</v>
       </c>
       <c r="F3" t="n">
-        <v>353.521575043377</v>
+        <v>285.3195817084329</v>
       </c>
       <c r="G3" t="n">
-        <v>353.521575043377</v>
+        <v>285.3195817084329</v>
       </c>
       <c r="H3" t="n">
         <v>285.3195817084329</v>
@@ -4421,31 +4421,31 @@
         <v>1221.432420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1046.604879873102</v>
+        <v>1221.432420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>897.8434684666579</v>
+        <v>814.0420374007307</v>
       </c>
       <c r="S3" t="n">
-        <v>830.6071048660405</v>
+        <v>746.8056738001133</v>
       </c>
       <c r="T3" t="n">
-        <v>825.1952208079457</v>
+        <v>741.3937897420185</v>
       </c>
       <c r="U3" t="n">
-        <v>420.9423321612924</v>
+        <v>741.1813051357692</v>
       </c>
       <c r="V3" t="n">
-        <v>406.2850925738983</v>
+        <v>726.5240655483751</v>
       </c>
       <c r="W3" t="n">
-        <v>373.5849482205361</v>
+        <v>693.823921195013</v>
       </c>
       <c r="X3" t="n">
-        <v>353.521575043377</v>
+        <v>673.7605480178538</v>
       </c>
       <c r="Y3" t="n">
-        <v>353.521575043377</v>
+        <v>673.7605480178538</v>
       </c>
     </row>
     <row r="4">
@@ -4455,28 +4455,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>289.1666383453244</v>
+        <v>564.6958905181907</v>
       </c>
       <c r="C4" t="n">
-        <v>415.1686441637602</v>
+        <v>690.6978963366265</v>
       </c>
       <c r="D4" t="n">
-        <v>528.4877882887603</v>
+        <v>804.0170404616266</v>
       </c>
       <c r="E4" t="n">
-        <v>646.3166925001733</v>
+        <v>921.8459446730396</v>
       </c>
       <c r="F4" t="n">
-        <v>770.6776650921088</v>
+        <v>1046.206917264975</v>
       </c>
       <c r="G4" t="n">
-        <v>924.084230978994</v>
+        <v>1046.206917264975</v>
       </c>
       <c r="H4" t="n">
-        <v>1093.600816138392</v>
+        <v>1215.723502424373</v>
       </c>
       <c r="I4" t="n">
-        <v>1314.733695074475</v>
+        <v>1215.723502424373</v>
       </c>
       <c r="J4" t="n">
         <v>1576.807243076824</v>
@@ -4509,22 +4509,22 @@
         <v>66</v>
       </c>
       <c r="T4" t="n">
-        <v>66</v>
+        <v>142.7078592869204</v>
       </c>
       <c r="U4" t="n">
-        <v>66</v>
+        <v>142.7078592869204</v>
       </c>
       <c r="V4" t="n">
-        <v>66</v>
+        <v>341.5292521728663</v>
       </c>
       <c r="W4" t="n">
-        <v>66</v>
+        <v>341.5292521728663</v>
       </c>
       <c r="X4" t="n">
-        <v>66</v>
+        <v>341.5292521728663</v>
       </c>
       <c r="Y4" t="n">
-        <v>177.4093006790322</v>
+        <v>452.9385528518986</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1243.993207924635</v>
+        <v>1107.328124213083</v>
       </c>
       <c r="C5" t="n">
-        <v>1194.018886467065</v>
+        <v>1057.353802755514</v>
       </c>
       <c r="D5" t="n">
-        <v>1183.575294810651</v>
+        <v>1046.9102110991</v>
       </c>
       <c r="E5" t="n">
-        <v>775.1275275309857</v>
+        <v>1042.502847859839</v>
       </c>
       <c r="F5" t="n">
-        <v>366.1481045936</v>
+        <v>633.5234249224528</v>
       </c>
       <c r="G5" t="n">
-        <v>362.3527790511594</v>
+        <v>225.6876953396081</v>
       </c>
       <c r="H5" t="n">
         <v>217.5971309926107</v>
@@ -4561,22 +4561,22 @@
         <v>457.3091130376557</v>
       </c>
       <c r="K5" t="n">
-        <v>1167.015479385524</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="L5" t="n">
-        <v>1359.180851496302</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="M5" t="n">
-        <v>1870.029680225237</v>
+        <v>968.1579417665907</v>
       </c>
       <c r="N5" t="n">
-        <v>2483.25</v>
+        <v>1227.900904947332</v>
       </c>
       <c r="O5" t="n">
-        <v>3300</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="P5" t="n">
-        <v>3300</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q5" t="n">
         <v>3300</v>
@@ -4585,25 +4585,25 @@
         <v>3046.587273910814</v>
       </c>
       <c r="S5" t="n">
-        <v>2950.781043807457</v>
+        <v>2546.740639767053</v>
       </c>
       <c r="T5" t="n">
-        <v>2358.179446101837</v>
+        <v>2221.514362390286</v>
       </c>
       <c r="U5" t="n">
-        <v>2106.440762719402</v>
+        <v>1969.775679007851</v>
       </c>
       <c r="V5" t="n">
-        <v>1874.268011035742</v>
+        <v>1737.602927324191</v>
       </c>
       <c r="W5" t="n">
-        <v>1633.486722166098</v>
+        <v>1496.821638454547</v>
       </c>
       <c r="X5" t="n">
-        <v>1439.262647963403</v>
+        <v>1302.597564251852</v>
       </c>
       <c r="Y5" t="n">
-        <v>1326.820796768649</v>
+        <v>1190.155713057098</v>
       </c>
     </row>
     <row r="6">
@@ -4613,76 +4613,76 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>66</v>
+        <v>2816.664325301065</v>
       </c>
       <c r="C6" t="n">
-        <v>66</v>
+        <v>2816.664325301065</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>2816.664325301065</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>2816.664325301065</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>2473.597413848664</v>
       </c>
       <c r="G6" t="n">
-        <v>66</v>
+        <v>2144.567579631464</v>
       </c>
       <c r="H6" t="n">
-        <v>66</v>
+        <v>2144.567579631464</v>
       </c>
       <c r="I6" t="n">
-        <v>66</v>
+        <v>2144.567579631464</v>
       </c>
       <c r="J6" t="n">
-        <v>189.9565201752989</v>
+        <v>2268.524099806763</v>
       </c>
       <c r="K6" t="n">
-        <v>379.1493362696824</v>
+        <v>2457.716915901147</v>
       </c>
       <c r="L6" t="n">
-        <v>650.4997978648825</v>
+        <v>2729.067377496347</v>
       </c>
       <c r="M6" t="n">
-        <v>736.5803396077417</v>
+        <v>2815.147919239206</v>
       </c>
       <c r="N6" t="n">
-        <v>869.8606242153101</v>
+        <v>2948.428203846775</v>
       </c>
       <c r="O6" t="n">
-        <v>1108.903075899029</v>
+        <v>3187.470655530493</v>
       </c>
       <c r="P6" t="n">
-        <v>1221.432420368536</v>
+        <v>3300</v>
       </c>
       <c r="Q6" t="n">
-        <v>1221.432420368536</v>
+        <v>3125.172459504566</v>
       </c>
       <c r="R6" t="n">
-        <v>1072.671008962092</v>
+        <v>2956.945814683942</v>
       </c>
       <c r="S6" t="n">
-        <v>1005.434645361474</v>
+        <v>2889.709451083324</v>
       </c>
       <c r="T6" t="n">
-        <v>595.9823572629755</v>
+        <v>2884.297567025229</v>
       </c>
       <c r="U6" t="n">
-        <v>595.7698726567262</v>
+        <v>2884.08508241898</v>
       </c>
       <c r="V6" t="n">
-        <v>581.1126330693321</v>
+        <v>2869.427842831586</v>
       </c>
       <c r="W6" t="n">
-        <v>144.3720846755659</v>
+        <v>2836.727698478224</v>
       </c>
       <c r="X6" t="n">
-        <v>66</v>
+        <v>2816.664325301065</v>
       </c>
       <c r="Y6" t="n">
-        <v>66</v>
+        <v>2816.664325301065</v>
       </c>
     </row>
     <row r="7">
@@ -4692,19 +4692,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1057.460933153428</v>
+        <v>1245.536612312233</v>
       </c>
       <c r="C7" t="n">
-        <v>1183.462938971864</v>
+        <v>1371.538618130669</v>
       </c>
       <c r="D7" t="n">
-        <v>1296.782083096864</v>
+        <v>1484.857762255669</v>
       </c>
       <c r="E7" t="n">
-        <v>1414.610987308277</v>
+        <v>1576.807243076824</v>
       </c>
       <c r="F7" t="n">
-        <v>1538.971959900212</v>
+        <v>1576.807243076824</v>
       </c>
       <c r="G7" t="n">
         <v>1576.807243076824</v>
@@ -4746,22 +4746,22 @@
         <v>66</v>
       </c>
       <c r="T7" t="n">
-        <v>66</v>
+        <v>254.0756791588049</v>
       </c>
       <c r="U7" t="n">
-        <v>312.5511926382866</v>
+        <v>500.6268717970915</v>
       </c>
       <c r="V7" t="n">
-        <v>511.3725855242326</v>
+        <v>699.4482646830375</v>
       </c>
       <c r="W7" t="n">
-        <v>683.26350378391</v>
+        <v>871.3391829427148</v>
       </c>
       <c r="X7" t="n">
-        <v>834.2942948081035</v>
+        <v>1022.369973966908</v>
       </c>
       <c r="Y7" t="n">
-        <v>945.7035954871358</v>
+        <v>1133.779274645941</v>
       </c>
     </row>
     <row r="8">
@@ -4771,76 +4771,76 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>703.2877201726793</v>
+        <v>689.325125933012</v>
       </c>
       <c r="C8" t="n">
-        <v>653.3133987151097</v>
+        <v>639.3508044754424</v>
       </c>
       <c r="D8" t="n">
-        <v>642.8698070586958</v>
+        <v>628.9072128190285</v>
       </c>
       <c r="E8" t="n">
-        <v>234.4220397790304</v>
+        <v>220.4594455393632</v>
       </c>
       <c r="F8" t="n">
-        <v>229.4830208820487</v>
+        <v>215.5204266423815</v>
       </c>
       <c r="G8" t="n">
-        <v>225.6876953396081</v>
+        <v>211.7251010999409</v>
       </c>
       <c r="H8" t="n">
-        <v>217.5971309926107</v>
+        <v>203.6345367529435</v>
       </c>
       <c r="I8" t="n">
         <v>66</v>
       </c>
       <c r="J8" t="n">
-        <v>66</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="K8" t="n">
-        <v>542.4308514963018</v>
+        <v>1167.015479385524</v>
       </c>
       <c r="L8" t="n">
-        <v>1359.180851496302</v>
+        <v>1737.331756443634</v>
       </c>
       <c r="M8" t="n">
-        <v>1870.029680225237</v>
+        <v>2248.180585172569</v>
       </c>
       <c r="N8" t="n">
-        <v>2483.25</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="O8" t="n">
-        <v>3300</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="P8" t="n">
-        <v>3300</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q8" t="n">
         <v>3300</v>
       </c>
       <c r="R8" t="n">
-        <v>3046.587273910814</v>
+        <v>3300</v>
       </c>
       <c r="S8" t="n">
-        <v>2546.740639767053</v>
+        <v>2800.153365856239</v>
       </c>
       <c r="T8" t="n">
-        <v>2358.179446101837</v>
+        <v>2207.551768150619</v>
       </c>
       <c r="U8" t="n">
-        <v>2106.440762719402</v>
+        <v>1955.813084768184</v>
       </c>
       <c r="V8" t="n">
-        <v>1874.268011035741</v>
+        <v>1319.599929044119</v>
       </c>
       <c r="W8" t="n">
-        <v>1633.486722166097</v>
+        <v>1078.818640174475</v>
       </c>
       <c r="X8" t="n">
-        <v>1035.222243922999</v>
+        <v>884.5945659717806</v>
       </c>
       <c r="Y8" t="n">
-        <v>922.7803927282447</v>
+        <v>772.1527147770267</v>
       </c>
     </row>
     <row r="9">
@@ -4850,19 +4850,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>124.3087114984067</v>
+        <v>932.3895195792148</v>
       </c>
       <c r="C9" t="n">
-        <v>66</v>
+        <v>932.3895195792148</v>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>741.1632657544849</v>
       </c>
       <c r="E9" t="n">
-        <v>66</v>
+        <v>395.0298342171994</v>
       </c>
       <c r="F9" t="n">
-        <v>66</v>
+        <v>395.0298342171994</v>
       </c>
       <c r="G9" t="n">
         <v>66</v>
@@ -4907,19 +4907,19 @@
         <v>1000.02276130338</v>
       </c>
       <c r="U9" t="n">
-        <v>595.7698726567262</v>
+        <v>999.8102766971302</v>
       </c>
       <c r="V9" t="n">
-        <v>581.1126330693321</v>
+        <v>985.1530371097361</v>
       </c>
       <c r="W9" t="n">
-        <v>144.3720846755659</v>
+        <v>952.452892756374</v>
       </c>
       <c r="X9" t="n">
-        <v>124.3087114984067</v>
+        <v>932.3895195792148</v>
       </c>
       <c r="Y9" t="n">
-        <v>124.3087114984067</v>
+        <v>932.3895195792148</v>
       </c>
     </row>
     <row r="10">
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>585.3718669188288</v>
+        <v>628.2731085283228</v>
       </c>
       <c r="C10" t="n">
-        <v>585.3718669188288</v>
+        <v>754.2751143467586</v>
       </c>
       <c r="D10" t="n">
-        <v>698.6910110438289</v>
+        <v>867.5942584717587</v>
       </c>
       <c r="E10" t="n">
-        <v>816.5199152552419</v>
+        <v>985.4231626831718</v>
       </c>
       <c r="F10" t="n">
-        <v>940.8808878471774</v>
+        <v>1109.784135275107</v>
       </c>
       <c r="G10" t="n">
-        <v>1094.287453734063</v>
+        <v>1263.190701161993</v>
       </c>
       <c r="H10" t="n">
-        <v>1263.80403889346</v>
+        <v>1432.70728632139</v>
       </c>
       <c r="I10" t="n">
-        <v>1263.80403889346</v>
+        <v>1432.70728632139</v>
       </c>
       <c r="J10" t="n">
         <v>1576.807243076824</v>
@@ -4980,25 +4980,25 @@
         <v>66</v>
       </c>
       <c r="S10" t="n">
-        <v>103.2502550941731</v>
+        <v>66</v>
       </c>
       <c r="T10" t="n">
-        <v>103.2502550941731</v>
+        <v>254.0756791588049</v>
       </c>
       <c r="U10" t="n">
-        <v>103.2502550941731</v>
+        <v>254.0756791588049</v>
       </c>
       <c r="V10" t="n">
-        <v>302.0716479801191</v>
+        <v>254.0756791588049</v>
       </c>
       <c r="W10" t="n">
-        <v>473.9625662397965</v>
+        <v>254.0756791588049</v>
       </c>
       <c r="X10" t="n">
-        <v>473.9625662397965</v>
+        <v>405.1064701829984</v>
       </c>
       <c r="Y10" t="n">
-        <v>585.3718669188288</v>
+        <v>516.5157708620306</v>
       </c>
     </row>
     <row r="11">
@@ -5008,10 +5008,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1021.044977321634</v>
+        <v>1208.256245745725</v>
       </c>
       <c r="C11" t="n">
-        <v>794.3029790963881</v>
+        <v>981.5142475204788</v>
       </c>
       <c r="D11" t="n">
         <v>794.3029790963881</v>
@@ -5035,16 +5035,16 @@
         <v>457.3091130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1167.015479385524</v>
+        <v>717.0520762183975</v>
       </c>
       <c r="L11" t="n">
-        <v>1983.765479385524</v>
+        <v>1533.802076218397</v>
       </c>
       <c r="M11" t="n">
-        <v>2248.180585172569</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="N11" t="n">
-        <v>2861.400904947332</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="O11" t="n">
         <v>2861.400904947332</v>
@@ -5056,28 +5056,28 @@
         <v>3300</v>
       </c>
       <c r="R11" t="n">
-        <v>3300</v>
+        <v>3273.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3027.426093128967</v>
+        <v>3001.286094312508</v>
       </c>
       <c r="T11" t="n">
-        <v>2662.097222696074</v>
+        <v>3001.286094312508</v>
       </c>
       <c r="U11" t="n">
-        <v>2233.590862545962</v>
+        <v>2954.542184378877</v>
       </c>
       <c r="V11" t="n">
-        <v>1824.650434094625</v>
+        <v>2545.60175592754</v>
       </c>
       <c r="W11" t="n">
-        <v>1407.101468457304</v>
+        <v>2128.052790290219</v>
       </c>
       <c r="X11" t="n">
-        <v>1036.109717486932</v>
+        <v>1757.061039319847</v>
       </c>
       <c r="Y11" t="n">
-        <v>1021.044977321634</v>
+        <v>1467.851511357417</v>
       </c>
     </row>
     <row r="12">
@@ -5108,25 +5108,25 @@
         <v>66</v>
       </c>
       <c r="I12" t="n">
-        <v>66</v>
+        <v>73.79487796756496</v>
       </c>
       <c r="J12" t="n">
-        <v>412.706520175299</v>
+        <v>420.5013981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>824.6493362696824</v>
+        <v>832.4442142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1122.720378378698</v>
+        <v>1326.544675832447</v>
       </c>
       <c r="M12" t="n">
-        <v>1431.550920121557</v>
+        <v>1635.375217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1787.581204729126</v>
+        <v>1991.405502182875</v>
       </c>
       <c r="O12" t="n">
-        <v>2249.373656412844</v>
+        <v>2453.197953866594</v>
       </c>
       <c r="P12" t="n">
         <v>2584.653000882351</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>207.7496180158189</v>
+        <v>178.3115880782802</v>
       </c>
       <c r="C13" t="n">
-        <v>207.7496180158189</v>
+        <v>178.3115880782802</v>
       </c>
       <c r="D13" t="n">
-        <v>146.6019230102073</v>
+        <v>178.3115880782802</v>
       </c>
       <c r="E13" t="n">
-        <v>90.05555448802895</v>
+        <v>168.9361651284484</v>
       </c>
       <c r="F13" t="n">
-        <v>90.05555448802895</v>
+        <v>119.0544924337596</v>
       </c>
       <c r="G13" t="n">
-        <v>69.80921828446326</v>
+        <v>98.80815623019389</v>
       </c>
       <c r="H13" t="n">
+        <v>94.99893794573063</v>
+      </c>
+      <c r="I13" t="n">
+        <v>142.8818168818135</v>
+      </c>
+      <c r="J13" t="n">
+        <v>330.7155575342649</v>
+      </c>
+      <c r="K13" t="n">
+        <v>266.5531597553325</v>
+      </c>
+      <c r="L13" t="n">
         <v>66</v>
       </c>
-      <c r="I13" t="n">
-        <v>113.8828789360829</v>
-      </c>
-      <c r="J13" t="n">
-        <v>301.7166195885342</v>
-      </c>
-      <c r="K13" t="n">
-        <v>301.7166195885342</v>
-      </c>
-      <c r="L13" t="n">
-        <v>301.7166195885342</v>
-      </c>
       <c r="M13" t="n">
-        <v>301.7166195885342</v>
+        <v>66</v>
       </c>
       <c r="N13" t="n">
-        <v>301.7166195885342</v>
+        <v>66</v>
       </c>
       <c r="O13" t="n">
-        <v>179.4629147137776</v>
+        <v>66</v>
       </c>
       <c r="P13" t="n">
-        <v>179.4629147137776</v>
+        <v>66</v>
       </c>
       <c r="Q13" t="n">
-        <v>179.4629147137776</v>
+        <v>66</v>
       </c>
       <c r="R13" t="n">
-        <v>179.4629147137776</v>
+        <v>66</v>
       </c>
       <c r="S13" t="n">
-        <v>179.4629147137776</v>
+        <v>66</v>
       </c>
       <c r="T13" t="n">
-        <v>194.2885938725825</v>
+        <v>80.82567915880486</v>
       </c>
       <c r="U13" t="n">
-        <v>267.5897865108691</v>
+        <v>154.1268717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>293.161179396815</v>
+        <v>179.6982646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>293.161179396815</v>
+        <v>178.3115880782802</v>
       </c>
       <c r="X13" t="n">
-        <v>270.4908304775145</v>
+        <v>178.3115880782802</v>
       </c>
       <c r="Y13" t="n">
-        <v>270.4908304775145</v>
+        <v>178.3115880782802</v>
       </c>
     </row>
     <row r="14">
@@ -5245,25 +5245,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>899.1653366548161</v>
+        <v>899.4261360340223</v>
       </c>
       <c r="C14" t="n">
-        <v>723.9384899447213</v>
+        <v>724.1992893239275</v>
       </c>
       <c r="D14" t="n">
-        <v>588.2423730357821</v>
+        <v>588.5031724149883</v>
       </c>
       <c r="E14" t="n">
-        <v>458.5824845439955</v>
+        <v>458.8432839232017</v>
       </c>
       <c r="F14" t="n">
-        <v>328.3909403944886</v>
+        <v>328.6517397736948</v>
       </c>
       <c r="G14" t="n">
-        <v>199.3430895995226</v>
+        <v>199.6038889787289</v>
       </c>
       <c r="H14" t="n">
-        <v>66</v>
+        <v>66.26079937920625</v>
       </c>
       <c r="I14" t="n">
         <v>66</v>
@@ -5275,10 +5275,10 @@
         <v>457.3091130376557</v>
       </c>
       <c r="L14" t="n">
-        <v>1274.059113037656</v>
+        <v>920.5817564436344</v>
       </c>
       <c r="M14" t="n">
-        <v>1784.907941766591</v>
+        <v>1431.430585172569</v>
       </c>
       <c r="N14" t="n">
         <v>2044.650904947332</v>
@@ -5299,22 +5299,22 @@
         <v>3078.941244644118</v>
       </c>
       <c r="T14" t="n">
-        <v>2764.86672634717</v>
+        <v>2765.127525726377</v>
       </c>
       <c r="U14" t="n">
-        <v>2387.87551771221</v>
+        <v>2388.136317091416</v>
       </c>
       <c r="V14" t="n">
-        <v>2030.450240776024</v>
+        <v>2030.711040155231</v>
       </c>
       <c r="W14" t="n">
-        <v>1664.416426653855</v>
+        <v>1664.677226033061</v>
       </c>
       <c r="X14" t="n">
-        <v>1344.939827198635</v>
+        <v>1345.200626577841</v>
       </c>
       <c r="Y14" t="n">
-        <v>1107.245450751356</v>
+        <v>1107.506250130562</v>
       </c>
     </row>
     <row r="15">
@@ -5354,16 +5354,16 @@
         <v>379.1493362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>923.7397978648826</v>
+        <v>650.4997978648825</v>
       </c>
       <c r="M15" t="n">
-        <v>1009.820339607742</v>
+        <v>736.5803396077417</v>
       </c>
       <c r="N15" t="n">
-        <v>1143.10062421531</v>
+        <v>869.8606242153101</v>
       </c>
       <c r="O15" t="n">
-        <v>1648.906383685571</v>
+        <v>1382.143075899029</v>
       </c>
       <c r="P15" t="n">
         <v>1761.435728155078</v>
@@ -5430,28 +5430,28 @@
         <v>827.5127230120967</v>
       </c>
       <c r="K16" t="n">
-        <v>814.8654767483158</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="L16" t="n">
-        <v>814.8654767483158</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="M16" t="n">
-        <v>814.8654767483158</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="N16" t="n">
-        <v>814.8654767483158</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="O16" t="n">
-        <v>814.8654767483158</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="P16" t="n">
-        <v>814.8654767483158</v>
+        <v>520.3830973995939</v>
       </c>
       <c r="Q16" t="n">
-        <v>608.3996037212187</v>
+        <v>66</v>
       </c>
       <c r="R16" t="n">
-        <v>153.2459390937934</v>
+        <v>66</v>
       </c>
       <c r="S16" t="n">
         <v>66</v>
@@ -5482,49 +5482,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>899.4261360340223</v>
+        <v>899.1653366548161</v>
       </c>
       <c r="C17" t="n">
-        <v>724.1992893239275</v>
+        <v>723.9384899447213</v>
       </c>
       <c r="D17" t="n">
-        <v>588.5031724149883</v>
+        <v>588.2423730357821</v>
       </c>
       <c r="E17" t="n">
-        <v>458.8432839232017</v>
+        <v>458.5824845439955</v>
       </c>
       <c r="F17" t="n">
-        <v>328.6517397736948</v>
+        <v>328.3909403944886</v>
       </c>
       <c r="G17" t="n">
-        <v>199.6038889787289</v>
+        <v>199.3430895995226</v>
       </c>
       <c r="H17" t="n">
-        <v>66.26079937920625</v>
+        <v>66</v>
       </c>
       <c r="I17" t="n">
         <v>66</v>
       </c>
       <c r="J17" t="n">
-        <v>457.3091130376557</v>
+        <v>66</v>
       </c>
       <c r="K17" t="n">
-        <v>457.3091130376557</v>
+        <v>542.4308514963018</v>
       </c>
       <c r="L17" t="n">
-        <v>457.3091130376557</v>
+        <v>1359.180851496302</v>
       </c>
       <c r="M17" t="n">
-        <v>968.1579417665907</v>
+        <v>1870.029680225237</v>
       </c>
       <c r="N17" t="n">
-        <v>1581.378261541354</v>
+        <v>2483.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2044.650904947332</v>
+        <v>2483.25</v>
       </c>
       <c r="P17" t="n">
-        <v>2861.400904947332</v>
+        <v>3300</v>
       </c>
       <c r="Q17" t="n">
         <v>3300</v>
@@ -5539,19 +5539,19 @@
         <v>2765.127525726377</v>
       </c>
       <c r="U17" t="n">
-        <v>2388.136317091416</v>
+        <v>2387.87551771221</v>
       </c>
       <c r="V17" t="n">
-        <v>2030.711040155231</v>
+        <v>2030.450240776024</v>
       </c>
       <c r="W17" t="n">
-        <v>1664.677226033061</v>
+        <v>1664.416426653855</v>
       </c>
       <c r="X17" t="n">
-        <v>1345.200626577841</v>
+        <v>1344.939827198635</v>
       </c>
       <c r="Y17" t="n">
-        <v>1107.506250130562</v>
+        <v>1107.245450751356</v>
       </c>
     </row>
     <row r="18">
@@ -5582,28 +5582,28 @@
         <v>66</v>
       </c>
       <c r="I18" t="n">
-        <v>66</v>
+        <v>124.284877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>189.9565201752989</v>
+        <v>248.2413981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>379.1493362696824</v>
+        <v>437.4342142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>745.9146332118499</v>
+        <v>708.7846758324474</v>
       </c>
       <c r="M18" t="n">
-        <v>831.9951749547092</v>
+        <v>1068.105217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>1238.515459562278</v>
+        <v>1201.385502182875</v>
       </c>
       <c r="O18" t="n">
-        <v>1750.797911245997</v>
+        <v>1713.667953866594</v>
       </c>
       <c r="P18" t="n">
-        <v>1863.327255715503</v>
+        <v>1826.197298336101</v>
       </c>
       <c r="Q18" t="n">
         <v>1863.327255715503</v>
@@ -5646,49 +5646,49 @@
         <v>411.8119797853441</v>
       </c>
       <c r="D19" t="n">
-        <v>402.1794362948841</v>
+        <v>411.8119797853441</v>
       </c>
       <c r="E19" t="n">
-        <v>402.1794362948841</v>
+        <v>411.8119797853441</v>
       </c>
       <c r="F19" t="n">
-        <v>403.7804088868195</v>
+        <v>413.4129523772796</v>
       </c>
       <c r="G19" t="n">
-        <v>434.4269747737048</v>
+        <v>444.0595182641649</v>
       </c>
       <c r="H19" t="n">
-        <v>481.1835599331024</v>
+        <v>490.8161034235625</v>
       </c>
       <c r="I19" t="n">
-        <v>579.5564388691853</v>
+        <v>589.1889823596454</v>
       </c>
       <c r="J19" t="n">
-        <v>817.8801795216366</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="K19" t="n">
-        <v>817.8801795216366</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="L19" t="n">
-        <v>817.8801795216366</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="M19" t="n">
-        <v>817.8801795216366</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="N19" t="n">
-        <v>817.8801795216366</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="O19" t="n">
-        <v>449.7533471185911</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>153.2459390937934</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="Q19" t="n">
-        <v>153.2459390937934</v>
+        <v>373.1296256125027</v>
       </c>
       <c r="R19" t="n">
-        <v>153.2459390937934</v>
+        <v>66</v>
       </c>
       <c r="S19" t="n">
         <v>66</v>
@@ -5719,25 +5719,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>899.1653366548161</v>
+        <v>899.4261360340223</v>
       </c>
       <c r="C20" t="n">
-        <v>723.9384899447213</v>
+        <v>724.1992893239275</v>
       </c>
       <c r="D20" t="n">
-        <v>588.2423730357821</v>
+        <v>588.5031724149883</v>
       </c>
       <c r="E20" t="n">
-        <v>458.5824845439955</v>
+        <v>458.8432839232017</v>
       </c>
       <c r="F20" t="n">
-        <v>328.3909403944886</v>
+        <v>328.6517397736948</v>
       </c>
       <c r="G20" t="n">
-        <v>199.3430895995226</v>
+        <v>199.6038889787289</v>
       </c>
       <c r="H20" t="n">
-        <v>66</v>
+        <v>66.26079937920625</v>
       </c>
       <c r="I20" t="n">
         <v>66</v>
@@ -5746,19 +5746,19 @@
         <v>457.3091130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>457.3091130376557</v>
+        <v>717.0520762183897</v>
       </c>
       <c r="L20" t="n">
-        <v>457.3091130376557</v>
+        <v>717.0520762183897</v>
       </c>
       <c r="M20" t="n">
-        <v>968.1579417665907</v>
+        <v>1227.900904947325</v>
       </c>
       <c r="N20" t="n">
-        <v>1581.378261541354</v>
+        <v>1227.900904947325</v>
       </c>
       <c r="O20" t="n">
-        <v>2044.650904947332</v>
+        <v>2044.650904947329</v>
       </c>
       <c r="P20" t="n">
         <v>2861.400904947332</v>
@@ -5767,28 +5767,28 @@
         <v>3300</v>
       </c>
       <c r="R20" t="n">
-        <v>3299.739200620793</v>
+        <v>3300</v>
       </c>
       <c r="S20" t="n">
-        <v>3078.680445264912</v>
+        <v>3078.941244644118</v>
       </c>
       <c r="T20" t="n">
-        <v>2764.86672634717</v>
+        <v>2765.127525726377</v>
       </c>
       <c r="U20" t="n">
-        <v>2387.87551771221</v>
+        <v>2388.136317091416</v>
       </c>
       <c r="V20" t="n">
-        <v>2030.450240776024</v>
+        <v>2030.711040155231</v>
       </c>
       <c r="W20" t="n">
-        <v>1664.416426653855</v>
+        <v>1664.677226033061</v>
       </c>
       <c r="X20" t="n">
-        <v>1344.939827198635</v>
+        <v>1345.200626577841</v>
       </c>
       <c r="Y20" t="n">
-        <v>1107.245450751356</v>
+        <v>1107.506250130562</v>
       </c>
     </row>
     <row r="21">
@@ -5831,16 +5831,16 @@
         <v>708.7846758324474</v>
       </c>
       <c r="M21" t="n">
-        <v>831.9951749547092</v>
+        <v>794.8652175753067</v>
       </c>
       <c r="N21" t="n">
-        <v>1238.515459562278</v>
+        <v>928.145502182875</v>
       </c>
       <c r="O21" t="n">
-        <v>1477.557911245997</v>
+        <v>1375.666383685571</v>
       </c>
       <c r="P21" t="n">
-        <v>1863.327255715503</v>
+        <v>1761.435728155078</v>
       </c>
       <c r="Q21" t="n">
         <v>1863.327255715503</v>
@@ -5904,22 +5904,22 @@
         <v>827.5127230120967</v>
       </c>
       <c r="K22" t="n">
-        <v>827.5127230120967</v>
+        <v>814.8654767483158</v>
       </c>
       <c r="L22" t="n">
-        <v>678.4747147719156</v>
+        <v>665.8274685081349</v>
       </c>
       <c r="M22" t="n">
-        <v>678.4747147719156</v>
+        <v>418.7248307277814</v>
       </c>
       <c r="N22" t="n">
-        <v>678.4747147719156</v>
+        <v>120.5580880291097</v>
       </c>
       <c r="O22" t="n">
-        <v>678.4747147719156</v>
+        <v>66</v>
       </c>
       <c r="P22" t="n">
-        <v>520.3830973995939</v>
+        <v>66</v>
       </c>
       <c r="Q22" t="n">
         <v>66</v>
@@ -5956,10 +5956,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>899.1653366548161</v>
+        <v>899.4261360340223</v>
       </c>
       <c r="C23" t="n">
-        <v>723.9384899447213</v>
+        <v>724.1992893239275</v>
       </c>
       <c r="D23" t="n">
         <v>588.2423730357821</v>
@@ -5989,43 +5989,43 @@
         <v>1983.765479385524</v>
       </c>
       <c r="M23" t="n">
-        <v>2494.614308114459</v>
+        <v>2044.650904947329</v>
       </c>
       <c r="N23" t="n">
-        <v>3107.834627889222</v>
+        <v>2044.650904947329</v>
       </c>
       <c r="O23" t="n">
-        <v>3107.834627889222</v>
+        <v>2044.650904947329</v>
       </c>
       <c r="P23" t="n">
-        <v>3107.834627889222</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>3300</v>
       </c>
       <c r="R23" t="n">
-        <v>3299.739200620793</v>
+        <v>3300</v>
       </c>
       <c r="S23" t="n">
-        <v>3078.680445264912</v>
+        <v>3078.941244644118</v>
       </c>
       <c r="T23" t="n">
-        <v>2764.86672634717</v>
+        <v>2765.127525726377</v>
       </c>
       <c r="U23" t="n">
-        <v>2387.87551771221</v>
+        <v>2388.136317091416</v>
       </c>
       <c r="V23" t="n">
-        <v>2030.450240776024</v>
+        <v>2030.711040155231</v>
       </c>
       <c r="W23" t="n">
-        <v>1664.416426653855</v>
+        <v>1664.677226033061</v>
       </c>
       <c r="X23" t="n">
-        <v>1344.939827198635</v>
+        <v>1345.200626577841</v>
       </c>
       <c r="Y23" t="n">
-        <v>1107.245450751356</v>
+        <v>1107.506250130562</v>
       </c>
     </row>
     <row r="24">
@@ -6056,28 +6056,28 @@
         <v>66</v>
       </c>
       <c r="I24" t="n">
-        <v>66</v>
+        <v>124.284877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>463.1965201752989</v>
+        <v>521.4813981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>925.6293362696823</v>
+        <v>983.9142142372473</v>
       </c>
       <c r="L24" t="n">
-        <v>1196.979797864882</v>
+        <v>1255.264675832447</v>
       </c>
       <c r="M24" t="n">
-        <v>1378.475174954709</v>
+        <v>1341.345217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>1511.755459562278</v>
+        <v>1474.625502182875</v>
       </c>
       <c r="O24" t="n">
-        <v>1750.797911245997</v>
+        <v>1713.667953866594</v>
       </c>
       <c r="P24" t="n">
-        <v>1863.327255715503</v>
+        <v>1826.197298336101</v>
       </c>
       <c r="Q24" t="n">
         <v>1863.327255715503</v>
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>408.5699739669084</v>
+        <v>385.7627485259578</v>
       </c>
       <c r="C25" t="n">
-        <v>411.8119797853441</v>
+        <v>389.0047543443936</v>
       </c>
       <c r="D25" t="n">
-        <v>411.8119797853441</v>
+        <v>379.3722108539335</v>
       </c>
       <c r="E25" t="n">
-        <v>411.8119797853441</v>
+        <v>374.3409938469067</v>
       </c>
       <c r="F25" t="n">
-        <v>413.4129523772796</v>
+        <v>375.9419664388422</v>
       </c>
       <c r="G25" t="n">
-        <v>444.0595182641649</v>
+        <v>406.5885323257274</v>
       </c>
       <c r="H25" t="n">
-        <v>490.8161034235625</v>
+        <v>453.345117485125</v>
       </c>
       <c r="I25" t="n">
-        <v>589.1889823596454</v>
+        <v>551.7179964212079</v>
       </c>
       <c r="J25" t="n">
-        <v>827.5127230120967</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="K25" t="n">
-        <v>827.5127230120967</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="L25" t="n">
-        <v>827.5127230120967</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="M25" t="n">
-        <v>779.7706793939014</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="N25" t="n">
-        <v>481.6039366952298</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="O25" t="n">
-        <v>481.6039366952298</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="P25" t="n">
-        <v>66</v>
+        <v>790.0417370736592</v>
       </c>
       <c r="Q25" t="n">
-        <v>66</v>
+        <v>608.3996037212187</v>
       </c>
       <c r="R25" t="n">
-        <v>66</v>
+        <v>153.2459390937934</v>
       </c>
       <c r="S25" t="n">
         <v>66</v>
@@ -6183,7 +6183,7 @@
         <v>408.5699739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>408.5699739669084</v>
+        <v>396.9888094725019</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1017.364977321634</v>
+        <v>277.1649250963515</v>
       </c>
       <c r="C26" t="n">
-        <v>790.622979096388</v>
+        <v>62.32</v>
       </c>
       <c r="D26" t="n">
-        <v>790.622979096388</v>
+        <v>62.32</v>
       </c>
       <c r="E26" t="n">
-        <v>609.44793908945</v>
+        <v>62.32</v>
       </c>
       <c r="F26" t="n">
-        <v>427.7412434247915</v>
+        <v>62.32</v>
       </c>
       <c r="G26" t="n">
-        <v>247.1782411146742</v>
+        <v>62.32</v>
       </c>
       <c r="H26" t="n">
         <v>62.32</v>
@@ -6220,22 +6220,22 @@
         <v>62.32</v>
       </c>
       <c r="K26" t="n">
-        <v>62.32</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L26" t="n">
-        <v>833.53</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="M26" t="n">
-        <v>833.53</v>
+        <v>2054.085195076803</v>
       </c>
       <c r="N26" t="n">
-        <v>1446.750319774763</v>
+        <v>2054.085195076803</v>
       </c>
       <c r="O26" t="n">
-        <v>2217.960319774777</v>
+        <v>2825.295195076814</v>
       </c>
       <c r="P26" t="n">
-        <v>2677.400904947332</v>
+        <v>2825.295195076814</v>
       </c>
       <c r="Q26" t="n">
         <v>3116</v>
@@ -6244,25 +6244,25 @@
         <v>3089.860001183541</v>
       </c>
       <c r="S26" t="n">
-        <v>3089.860001183541</v>
+        <v>2817.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2724.531130750648</v>
+        <v>2451.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2296.024770600536</v>
+        <v>2023.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>1887.084342149199</v>
+        <v>1614.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1887.084342149199</v>
+        <v>1196.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1516.092591178827</v>
+        <v>825.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1226.883063216397</v>
+        <v>536.760190708043</v>
       </c>
     </row>
     <row r="27">
@@ -6299,13 +6299,13 @@
         <v>416.8213981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.9399167834981</v>
+        <v>828.7642142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1119.040378378698</v>
+        <v>1322.864675832448</v>
       </c>
       <c r="M27" t="n">
-        <v>1427.870920121557</v>
+        <v>1631.695217575307</v>
       </c>
       <c r="N27" t="n">
         <v>1783.901204729126</v>
@@ -6381,22 +6381,22 @@
         <v>406.5389893823511</v>
       </c>
       <c r="L28" t="n">
-        <v>205.9858296270186</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="M28" t="n">
-        <v>205.9858296270186</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="N28" t="n">
-        <v>205.9858296270186</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="O28" t="n">
-        <v>62.32</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="P28" t="n">
-        <v>62.32</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.32</v>
+        <v>406.5389893823511</v>
       </c>
       <c r="R28" t="n">
         <v>62.32</v>
@@ -6457,19 +6457,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K29" t="n">
-        <v>636.5331712083649</v>
+        <v>1162.086706495332</v>
       </c>
       <c r="L29" t="n">
-        <v>624.1320762183583</v>
+        <v>1372.878510524729</v>
       </c>
       <c r="M29" t="n">
-        <v>1134.980904947293</v>
+        <v>1883.727339253664</v>
       </c>
       <c r="N29" t="n">
-        <v>1134.980904947293</v>
+        <v>1906.190904947317</v>
       </c>
       <c r="O29" t="n">
-        <v>1906.190904947313</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P29" t="n">
         <v>2677.400904947332</v>
@@ -6533,25 +6533,25 @@
         <v>62.32</v>
       </c>
       <c r="J30" t="n">
-        <v>472.3865201752989</v>
+        <v>186.2765201752989</v>
       </c>
       <c r="K30" t="n">
-        <v>661.5793362696824</v>
+        <v>375.4693362696823</v>
       </c>
       <c r="L30" t="n">
-        <v>932.9297978648824</v>
+        <v>646.8197978648825</v>
       </c>
       <c r="M30" t="n">
-        <v>1019.010339607742</v>
+        <v>732.9003396077418</v>
       </c>
       <c r="N30" t="n">
-        <v>1311.105762592581</v>
+        <v>910.2342350321554</v>
       </c>
       <c r="O30" t="n">
-        <v>1550.1482142763</v>
+        <v>1149.276686715874</v>
       </c>
       <c r="P30" t="n">
-        <v>1662.677558745806</v>
+        <v>1547.916031185381</v>
       </c>
       <c r="Q30" t="n">
         <v>1662.677558745806</v>
@@ -6621,22 +6621,22 @@
         <v>980.6318436307025</v>
       </c>
       <c r="M31" t="n">
-        <v>746.6605189816622</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="N31" t="n">
-        <v>746.6605189816622</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="O31" t="n">
-        <v>746.6605189816622</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="P31" t="n">
-        <v>344.1878954177456</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="Q31" t="n">
-        <v>62.32</v>
+        <v>578.4569774585925</v>
       </c>
       <c r="R31" t="n">
-        <v>62.32</v>
+        <v>136.4346259624803</v>
       </c>
       <c r="S31" t="n">
         <v>62.32</v>
@@ -6667,46 +6667,46 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>820.4766410845275</v>
+        <v>816.6974578669373</v>
       </c>
       <c r="C32" t="n">
-        <v>658.3811075057457</v>
+        <v>654.6019242881555</v>
       </c>
       <c r="D32" t="n">
-        <v>535.8163037281197</v>
+        <v>532.0371205105295</v>
       </c>
       <c r="E32" t="n">
-        <v>419.2877283676463</v>
+        <v>415.5085451500561</v>
       </c>
       <c r="F32" t="n">
-        <v>302.2274973494525</v>
+        <v>298.4483141318623</v>
       </c>
       <c r="G32" t="n">
-        <v>186.3109596857998</v>
+        <v>182.5317764682095</v>
       </c>
       <c r="H32" t="n">
-        <v>66.09918321759025</v>
+        <v>62.32</v>
       </c>
       <c r="I32" t="n">
         <v>62.32</v>
       </c>
       <c r="J32" t="n">
-        <v>373.7211876853623</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>1082.178781143038</v>
+        <v>634.082358956508</v>
       </c>
       <c r="L32" t="n">
-        <v>1292.970585172545</v>
+        <v>634.082358956508</v>
       </c>
       <c r="M32" t="n">
-        <v>1292.970585172545</v>
+        <v>1144.931187685443</v>
       </c>
       <c r="N32" t="n">
-        <v>1906.190904947308</v>
+        <v>1758.151507460206</v>
       </c>
       <c r="O32" t="n">
-        <v>2677.400904947332</v>
+        <v>2529.361507460225</v>
       </c>
       <c r="P32" t="n">
         <v>2677.400904947332</v>
@@ -6724,19 +6724,19 @@
         <v>2607.390151989003</v>
       </c>
       <c r="U32" t="n">
-        <v>2243.530256485356</v>
+        <v>2239.751073267766</v>
       </c>
       <c r="V32" t="n">
-        <v>1899.236292680483</v>
+        <v>1895.457109462893</v>
       </c>
       <c r="W32" t="n">
-        <v>1546.333791689627</v>
+        <v>1542.554608472037</v>
       </c>
       <c r="X32" t="n">
-        <v>1239.98850536572</v>
+        <v>1236.20932214813</v>
       </c>
       <c r="Y32" t="n">
-        <v>1015.425442049754</v>
+        <v>1011.646258832164</v>
       </c>
     </row>
     <row r="33">
@@ -6767,28 +6767,28 @@
         <v>62.32</v>
       </c>
       <c r="I33" t="n">
-        <v>62.32</v>
+        <v>133.474877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>186.2765201752989</v>
+        <v>257.4313981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>375.4693362696823</v>
+        <v>705.632947086528</v>
       </c>
       <c r="L33" t="n">
-        <v>805.6349362421532</v>
+        <v>976.9834086817281</v>
       </c>
       <c r="M33" t="n">
-        <v>891.7154779850125</v>
+        <v>1063.063950424587</v>
       </c>
       <c r="N33" t="n">
-        <v>1024.995762592581</v>
+        <v>1196.344235032156</v>
       </c>
       <c r="O33" t="n">
-        <v>1264.0382142763</v>
+        <v>1435.386686715874</v>
       </c>
       <c r="P33" t="n">
-        <v>1662.677558745806</v>
+        <v>1547.916031185381</v>
       </c>
       <c r="Q33" t="n">
         <v>1662.677558745806</v>
@@ -6855,25 +6855,25 @@
         <v>980.6318436307025</v>
       </c>
       <c r="L34" t="n">
-        <v>980.6318436307025</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="M34" t="n">
-        <v>746.6605189816622</v>
+        <v>610.7538238727943</v>
       </c>
       <c r="N34" t="n">
-        <v>746.6605189816622</v>
+        <v>325.7183943054358</v>
       </c>
       <c r="O34" t="n">
-        <v>577.6864102307611</v>
+        <v>62.32</v>
       </c>
       <c r="P34" t="n">
-        <v>577.6864102307611</v>
+        <v>62.32</v>
       </c>
       <c r="Q34" t="n">
-        <v>136.4346259624803</v>
+        <v>62.32</v>
       </c>
       <c r="R34" t="n">
-        <v>136.4346259624803</v>
+        <v>62.32</v>
       </c>
       <c r="S34" t="n">
         <v>62.32</v>
@@ -6928,25 +6928,25 @@
         <v>62.32</v>
       </c>
       <c r="J35" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>770.7775934576761</v>
+        <v>1162.086706495332</v>
       </c>
       <c r="L35" t="n">
-        <v>759.6252713578607</v>
+        <v>1556.995688280981</v>
       </c>
       <c r="M35" t="n">
-        <v>1270.474100086796</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N35" t="n">
-        <v>1883.694419861559</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O35" t="n">
-        <v>2654.904419861599</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P35" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q35" t="n">
         <v>3116</v>
@@ -7004,28 +7004,28 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>62.32</v>
+        <v>133.474877967565</v>
       </c>
       <c r="J36" t="n">
-        <v>186.2765201752989</v>
+        <v>257.4313981428639</v>
       </c>
       <c r="K36" t="n">
-        <v>534.2844746469532</v>
+        <v>446.6242142372473</v>
       </c>
       <c r="L36" t="n">
-        <v>805.6349362421532</v>
+        <v>717.9746758324475</v>
       </c>
       <c r="M36" t="n">
-        <v>891.7154779850125</v>
+        <v>804.0552175753068</v>
       </c>
       <c r="N36" t="n">
-        <v>1024.995762592581</v>
+        <v>1223.445502182875</v>
       </c>
       <c r="O36" t="n">
-        <v>1264.0382142763</v>
+        <v>1462.487953866594</v>
       </c>
       <c r="P36" t="n">
-        <v>1662.677558745806</v>
+        <v>1575.017298336101</v>
       </c>
       <c r="Q36" t="n">
         <v>1662.677558745806</v>
@@ -7098,19 +7098,19 @@
         <v>980.6318436307025</v>
       </c>
       <c r="N37" t="n">
-        <v>695.596414063344</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="O37" t="n">
-        <v>695.596414063344</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="P37" t="n">
-        <v>695.596414063344</v>
+        <v>945.5941357643931</v>
       </c>
       <c r="Q37" t="n">
-        <v>254.3446297950632</v>
+        <v>504.3423514961122</v>
       </c>
       <c r="R37" t="n">
-        <v>136.4346259624803</v>
+        <v>62.32</v>
       </c>
       <c r="S37" t="n">
         <v>62.32</v>
@@ -7141,16 +7141,16 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>816.6974578669373</v>
+        <v>820.4766410845275</v>
       </c>
       <c r="C38" t="n">
-        <v>654.6019242881555</v>
+        <v>658.3811075057457</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0371205105295</v>
+        <v>535.8163037281197</v>
       </c>
       <c r="E38" t="n">
-        <v>415.5085451500561</v>
+        <v>419.2877283676463</v>
       </c>
       <c r="F38" t="n">
         <v>298.4483141318623</v>
@@ -7165,22 +7165,22 @@
         <v>62.32</v>
       </c>
       <c r="J38" t="n">
-        <v>301.4714540091902</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K38" t="n">
-        <v>1009.929047466866</v>
+        <v>1163.335479385524</v>
       </c>
       <c r="L38" t="n">
-        <v>1220.720851496244</v>
+        <v>1150.934384395518</v>
       </c>
       <c r="M38" t="n">
-        <v>1731.56968022518</v>
+        <v>1661.783213124453</v>
       </c>
       <c r="N38" t="n">
-        <v>2344.789999999943</v>
+        <v>2275.003532899216</v>
       </c>
       <c r="O38" t="n">
-        <v>3116</v>
+        <v>2344.789999999957</v>
       </c>
       <c r="P38" t="n">
         <v>3116</v>
@@ -7207,10 +7207,10 @@
         <v>1546.333791689627</v>
       </c>
       <c r="X38" t="n">
-        <v>1236.20932214813</v>
+        <v>1239.98850536572</v>
       </c>
       <c r="Y38" t="n">
-        <v>1011.646258832164</v>
+        <v>1015.425442049754</v>
       </c>
     </row>
     <row r="39">
@@ -7250,19 +7250,19 @@
         <v>446.6242142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>1004.084675832447</v>
+        <v>976.9834086817281</v>
       </c>
       <c r="M39" t="n">
-        <v>1090.165217575307</v>
+        <v>1063.063950424587</v>
       </c>
       <c r="N39" t="n">
-        <v>1223.445502182875</v>
+        <v>1196.344235032156</v>
       </c>
       <c r="O39" t="n">
-        <v>1462.487953866594</v>
+        <v>1435.386686715874</v>
       </c>
       <c r="P39" t="n">
-        <v>1662.677558745806</v>
+        <v>1547.916031185381</v>
       </c>
       <c r="Q39" t="n">
         <v>1662.677558745806</v>
@@ -7329,25 +7329,25 @@
         <v>980.6318436307025</v>
       </c>
       <c r="L40" t="n">
-        <v>980.6318436307025</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="M40" t="n">
-        <v>980.6318436307025</v>
+        <v>823.9426790937555</v>
       </c>
       <c r="N40" t="n">
-        <v>980.6318436307025</v>
+        <v>538.907249526397</v>
       </c>
       <c r="O40" t="n">
-        <v>625.6363243589702</v>
+        <v>538.907249526397</v>
       </c>
       <c r="P40" t="n">
-        <v>504.3423514961122</v>
+        <v>136.4346259624803</v>
       </c>
       <c r="Q40" t="n">
-        <v>504.3423514961122</v>
+        <v>136.4346259624803</v>
       </c>
       <c r="R40" t="n">
-        <v>62.32</v>
+        <v>136.4346259624803</v>
       </c>
       <c r="S40" t="n">
         <v>62.32</v>
@@ -7378,13 +7378,13 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>754.2252088231089</v>
+        <v>1257.091742004788</v>
       </c>
       <c r="C41" t="n">
-        <v>754.2252088231089</v>
+        <v>982.8749963047944</v>
       </c>
       <c r="D41" t="n">
-        <v>519.5391929242708</v>
+        <v>748.1889804059563</v>
       </c>
       <c r="E41" t="n">
         <v>519.5391929242708</v>
@@ -7402,22 +7402,22 @@
         <v>62.32</v>
       </c>
       <c r="J41" t="n">
-        <v>62.32</v>
+        <v>72.41539009576594</v>
       </c>
       <c r="K41" t="n">
-        <v>772.0263663478684</v>
+        <v>782.1217564436344</v>
       </c>
       <c r="L41" t="n">
-        <v>1543.236366347868</v>
+        <v>1553.331756443634</v>
       </c>
       <c r="M41" t="n">
-        <v>1543.236366347868</v>
+        <v>2064.180585172569</v>
       </c>
       <c r="N41" t="n">
-        <v>1543.236366347868</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>2314.446366347964</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>2677.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>3116</v>
       </c>
       <c r="R41" t="n">
-        <v>3042.385253708793</v>
+        <v>3104.384896431374</v>
       </c>
       <c r="S41" t="n">
-        <v>2722.336599363012</v>
+        <v>2784.336242085593</v>
       </c>
       <c r="T41" t="n">
-        <v>2338.984318083653</v>
+        <v>2784.336242085593</v>
       </c>
       <c r="U41" t="n">
-        <v>1863.003210458794</v>
+        <v>2784.336242085593</v>
       </c>
       <c r="V41" t="n">
-        <v>1863.003210458794</v>
+        <v>2784.336242085593</v>
       </c>
       <c r="W41" t="n">
-        <v>1397.979497346726</v>
+        <v>2319.312528973524</v>
       </c>
       <c r="X41" t="n">
-        <v>1397.979497346726</v>
+        <v>1900.846030528405</v>
       </c>
       <c r="Y41" t="n">
-        <v>1061.295221909548</v>
+        <v>1564.161755091227</v>
       </c>
     </row>
     <row r="42">
@@ -7457,19 +7457,19 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>887.1497623662093</v>
+        <v>950.0680158785851</v>
       </c>
       <c r="C42" t="n">
-        <v>702.2003558555838</v>
+        <v>765.1186093679596</v>
       </c>
       <c r="D42" t="n">
-        <v>530.5461266659852</v>
+        <v>593.464380178361</v>
       </c>
       <c r="E42" t="n">
-        <v>530.5461266659852</v>
+        <v>427.1289284390554</v>
       </c>
       <c r="F42" t="n">
-        <v>367.2771950115641</v>
+        <v>263.8599967846343</v>
       </c>
       <c r="G42" t="n">
         <v>218.0453405923446</v>
@@ -7487,46 +7487,46 @@
         <v>727.9093362696824</v>
       </c>
       <c r="L42" t="n">
-        <v>1175.479797864883</v>
+        <v>1038.969200185284</v>
       </c>
       <c r="M42" t="n">
-        <v>1261.560339607742</v>
+        <v>1301.269741928143</v>
       </c>
       <c r="N42" t="n">
-        <v>1566.6938493883</v>
+        <v>1610.770026535711</v>
       </c>
       <c r="O42" t="n">
-        <v>1981.956301072019</v>
+        <v>2026.03247821943</v>
       </c>
       <c r="P42" t="n">
-        <v>2270.705645541526</v>
+        <v>2314.781822688937</v>
       </c>
       <c r="Q42" t="n">
-        <v>2275.577173101951</v>
+        <v>2319.653350249362</v>
       </c>
       <c r="R42" t="n">
-        <v>1902.573337453083</v>
+        <v>2319.653350249362</v>
       </c>
       <c r="S42" t="n">
-        <v>1611.094549610041</v>
+        <v>2319.653350249362</v>
       </c>
       <c r="T42" t="n">
-        <v>1611.094549610041</v>
+        <v>2089.999041948843</v>
       </c>
       <c r="U42" t="n">
-        <v>1386.639640761368</v>
+        <v>1865.54413310017</v>
       </c>
       <c r="V42" t="n">
-        <v>1386.639640761368</v>
+        <v>1626.644469270351</v>
       </c>
       <c r="W42" t="n">
-        <v>1355.083229246534</v>
+        <v>1626.644469270351</v>
       </c>
       <c r="X42" t="n">
-        <v>1110.777431826951</v>
+        <v>1382.338671850768</v>
       </c>
       <c r="Y42" t="n">
-        <v>887.1497623662093</v>
+        <v>1158.711002390026</v>
       </c>
     </row>
     <row r="43">
@@ -7557,55 +7557,55 @@
         <v>62.32</v>
       </c>
       <c r="I43" t="n">
-        <v>63.67287893608291</v>
+        <v>62.32</v>
       </c>
       <c r="J43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="K43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="L43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="M43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="N43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="O43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="P43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="Q43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="R43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="S43" t="n">
-        <v>145.7647672981565</v>
+        <v>94.66804697601791</v>
       </c>
       <c r="T43" t="n">
-        <v>145.7647672981565</v>
+        <v>62.32</v>
       </c>
       <c r="U43" t="n">
-        <v>172.5359599364431</v>
+        <v>62.32</v>
       </c>
       <c r="V43" t="n">
-        <v>172.5359599364431</v>
+        <v>62.32</v>
       </c>
       <c r="W43" t="n">
-        <v>172.5359599364431</v>
+        <v>62.32</v>
       </c>
       <c r="X43" t="n">
-        <v>172.5359599364431</v>
+        <v>62.32</v>
       </c>
       <c r="Y43" t="n">
-        <v>172.5359599364431</v>
+        <v>62.32</v>
       </c>
     </row>
     <row r="44">
@@ -7615,25 +7615,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>495.0921709995488</v>
+        <v>963.8064779202939</v>
       </c>
       <c r="C44" t="n">
-        <v>495.0921709995488</v>
+        <v>573.4281160586838</v>
       </c>
       <c r="D44" t="n">
-        <v>495.0921709995488</v>
+        <v>573.4281160586838</v>
       </c>
       <c r="E44" t="n">
-        <v>150.2807673562471</v>
+        <v>407.6630593010221</v>
       </c>
       <c r="F44" t="n">
-        <v>150.2807673562471</v>
+        <v>62.32</v>
       </c>
       <c r="G44" t="n">
-        <v>150.2807673562471</v>
+        <v>62.32</v>
       </c>
       <c r="H44" t="n">
-        <v>150.2807673562471</v>
+        <v>62.32</v>
       </c>
       <c r="I44" t="n">
         <v>62.32</v>
@@ -7642,19 +7642,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>453.6291130376557</v>
+        <v>1134.98090494722</v>
       </c>
       <c r="L44" t="n">
-        <v>1224.839113037656</v>
+        <v>1906.19090494722</v>
       </c>
       <c r="M44" t="n">
-        <v>1735.68794176659</v>
+        <v>1906.19090494722</v>
       </c>
       <c r="N44" t="n">
-        <v>2348.908261541354</v>
+        <v>1906.19090494722</v>
       </c>
       <c r="O44" t="n">
-        <v>2348.908261541354</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>2677.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3116</v>
       </c>
       <c r="R44" t="n">
-        <v>2926.223637547178</v>
+        <v>3116</v>
       </c>
       <c r="S44" t="n">
-        <v>2926.223637547178</v>
+        <v>3116</v>
       </c>
       <c r="T44" t="n">
-        <v>2397.258403477921</v>
+        <v>3116</v>
       </c>
       <c r="U44" t="n">
-        <v>1805.115679691446</v>
+        <v>2523.857276213525</v>
       </c>
       <c r="V44" t="n">
-        <v>1232.538887603745</v>
+        <v>1951.280484125823</v>
       </c>
       <c r="W44" t="n">
-        <v>947.9380625983431</v>
+        <v>1951.280484125823</v>
       </c>
       <c r="X44" t="n">
-        <v>947.9380625983431</v>
+        <v>1416.652369519088</v>
       </c>
       <c r="Y44" t="n">
-        <v>495.0921709995488</v>
+        <v>963.8064779202939</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1183.20851790796</v>
+        <v>519.114240744311</v>
       </c>
       <c r="C45" t="n">
-        <v>882.0974952357183</v>
+        <v>218.0032180720692</v>
       </c>
       <c r="D45" t="n">
-        <v>882.0974952357183</v>
+        <v>218.0032180720692</v>
       </c>
       <c r="E45" t="n">
-        <v>599.6004273347964</v>
+        <v>218.0032180720692</v>
       </c>
       <c r="F45" t="n">
-        <v>599.6004273347964</v>
+        <v>218.0032180720692</v>
       </c>
       <c r="G45" t="n">
-        <v>334.2069567539608</v>
+        <v>218.0032180720692</v>
       </c>
       <c r="H45" t="n">
-        <v>62.32</v>
+        <v>218.0032180720692</v>
       </c>
       <c r="I45" t="n">
         <v>62.32</v>
       </c>
       <c r="J45" t="n">
-        <v>248.6465201752989</v>
+        <v>232.4129771483846</v>
       </c>
       <c r="K45" t="n">
-        <v>500.2093362696824</v>
+        <v>421.605793242768</v>
       </c>
       <c r="L45" t="n">
-        <v>833.9297978648824</v>
+        <v>755.3262548379681</v>
       </c>
       <c r="M45" t="n">
-        <v>982.3803396077417</v>
+        <v>903.7767965808273</v>
       </c>
       <c r="N45" t="n">
-        <v>1161.797081188396</v>
+        <v>1099.427081188396</v>
       </c>
       <c r="O45" t="n">
-        <v>1463.209532872115</v>
+        <v>1400.839532872114</v>
       </c>
       <c r="P45" t="n">
         <v>1575.738877341621</v>
       </c>
       <c r="Q45" t="n">
-        <v>1575.738877341621</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="R45" t="n">
-        <v>1575.738877341621</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="S45" t="n">
-        <v>1575.738877341621</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="T45" t="n">
-        <v>1575.738877341621</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="U45" t="n">
-        <v>1538.269797899394</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="V45" t="n">
-        <v>1183.20851790796</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="W45" t="n">
-        <v>1183.20851790796</v>
+        <v>1464.547700482551</v>
       </c>
       <c r="X45" t="n">
-        <v>1183.20851790796</v>
+        <v>1183.708129039726</v>
       </c>
       <c r="Y45" t="n">
-        <v>1183.20851790796</v>
+        <v>843.9188434173682</v>
       </c>
     </row>
     <row r="46">
@@ -7967,13 +7967,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>158.9610829645592</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>811.3480930837773</v>
       </c>
       <c r="N2" t="n">
         <v>1096.663422488788</v>
@@ -7982,7 +7982,7 @@
         <v>895.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>825.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q2" t="n">
         <v>615.8520732695737</v>
@@ -8204,25 +8204,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>194.106436475533</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>1096.663422488788</v>
+        <v>739.6155875453319</v>
       </c>
       <c r="O5" t="n">
         <v>895.2478695740924</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2870600406814136</v>
+        <v>825.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,13 +8438,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>481.2432843396987</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>825</v>
+        <v>576.0770475334448</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8453,13 +8453,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>895.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8678,19 +8678,19 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>262.3666294754967</v>
       </c>
       <c r="L11" t="n">
         <v>825</v>
       </c>
       <c r="M11" t="n">
-        <v>811.3480930837773</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>895.2478695740924</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8918,13 +8918,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>825</v>
+        <v>467.9521650565442</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N14" t="n">
-        <v>739.6155875453319</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
         <v>895.2478695740924</v>
@@ -9149,13 +9149,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>481.2432843396987</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,13 +9164,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>538.2000346306365</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
         <v>825.2870600406815</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,7 +9389,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>262.366629475489</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -9398,13 +9398,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N20" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O20" t="n">
-        <v>538.2000346306365</v>
+        <v>895.2478695740963</v>
       </c>
       <c r="P20" t="n">
-        <v>825.2870600406815</v>
+        <v>825.2870600406853</v>
       </c>
       <c r="Q20" t="n">
         <v>615.8520732695737</v>
@@ -9632,19 +9632,19 @@
         <v>825</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>605.7625575027259</v>
       </c>
       <c r="N23" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O23" t="n">
         <v>70.24786957409245</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>825.2870600406853</v>
       </c>
       <c r="Q23" t="n">
-        <v>366.9291208030185</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,25 +9863,25 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>779</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O26" t="n">
-        <v>849.2478695741063</v>
+        <v>849.2478695741031</v>
       </c>
       <c r="P26" t="n">
-        <v>464.3684592048789</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>466.4639014216129</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,22 +10100,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>184.7515739098073</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>224.1859859891026</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
-        <v>477.2489580698352</v>
+        <v>499.9394284674647</v>
       </c>
       <c r="O29" t="n">
-        <v>849.2478695741122</v>
+        <v>849.2478695741081</v>
       </c>
       <c r="P29" t="n">
-        <v>779.2870600407012</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10334,25 +10334,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>349.5896604727291</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
-        <v>716.8751175230994</v>
+        <v>182.2760059786388</v>
       </c>
       <c r="L32" t="n">
-        <v>224.1859859892122</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>849.2478695741167</v>
+        <v>849.2478695741113</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>162.3481635529187</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10571,13 +10571,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J35" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>406.4619919677929</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
@@ -10586,13 +10586,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>849.2478695741331</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>466.0401712915909</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>276.6101315068987</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>224.1859859890845</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,10 +10823,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>849.2478695741504</v>
+        <v>140.7392504839324</v>
       </c>
       <c r="P38" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407249</v>
       </c>
       <c r="Q38" t="n">
         <v>172.8226843274854</v>
@@ -11045,25 +11045,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>45.24036997818725</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>778.9999999999999</v>
+        <v>779</v>
       </c>
       <c r="M41" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>849.2478695741886</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>366.9078061006499</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11285,22 +11285,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>688.2341332419844</v>
       </c>
       <c r="L44" t="n">
         <v>779</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
-        <v>70.24786957409245</v>
+        <v>849.2478695742059</v>
       </c>
       <c r="P44" t="n">
-        <v>332.0978109558117</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -23223,13 +23223,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -23271,16 +23271,16 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>377.9448257143163</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -23292,7 +23292,7 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>271.4033399191614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -23381,19 +23381,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
         <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>46.69923611662308</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -23408,10 +23408,10 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>295.6316114025499</v>
@@ -23420,7 +23420,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>294.4143962530059</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P13" t="n">
         <v>462.4478973282775</v>
@@ -23444,10 +23444,10 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>22.44364543010755</v>
       </c>
       <c r="Y13" t="n">
         <v>62.46535284946236</v>
@@ -23645,7 +23645,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12.52077380114304</v>
       </c>
       <c r="L16" t="n">
         <v>147.5476281577792</v>
@@ -23660,16 +23660,16 @@
         <v>364.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>411.4478973282775</v>
+        <v>107.3895679718997</v>
       </c>
       <c r="Q16" t="n">
-        <v>245.4380521287718</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>450.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>86.37347970285543</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23861,7 +23861,7 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>9.53621805555548</v>
       </c>
       <c r="E19" t="n">
         <v>4.98090483695654</v>
@@ -23894,19 +23894,19 @@
         <v>295.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>364.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>117.9055633837277</v>
+        <v>411.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>449.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>450.6021279811511</v>
+        <v>146.5437986247734</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>86.37347970285543</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -24119,25 +24119,25 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>12.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>244.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>295.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>364.445564079015</v>
+        <v>310.4330569301963</v>
       </c>
       <c r="P22" t="n">
-        <v>254.937196129679</v>
+        <v>411.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>449.839266425598</v>
       </c>
       <c r="R22" t="n">
         <v>450.6021279811511</v>
@@ -24329,16 +24329,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>11.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>9.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>4.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24362,25 +24362,25 @@
         <v>147.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>197.3669882205366</v>
+        <v>244.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>295.1850752716849</v>
       </c>
       <c r="O25" t="n">
         <v>364.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>411.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>449.839266425598</v>
+        <v>270.0135544066819</v>
       </c>
       <c r="R25" t="n">
-        <v>450.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>86.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>11.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -24408,25 +24408,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>49.57640791975973</v>
+        <v>0</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>11.77810239760592</v>
       </c>
       <c r="D26" t="n">
         <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24471,7 +24471,7 @@
         <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>413.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
         <v>295.6316114025499</v>
@@ -24605,7 +24605,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>273.2163927482665</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>462.4478973282775</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24836,7 +24836,7 @@
         <v>134.5476281577792</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>231.6316114025499</v>
       </c>
       <c r="N31" t="n">
         <v>282.1850752716849</v>
@@ -24845,16 +24845,16 @@
         <v>351.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>398.4478973282775</v>
       </c>
       <c r="Q31" t="n">
-        <v>157.7900499620299</v>
+        <v>38.68614891520912</v>
       </c>
       <c r="R31" t="n">
-        <v>437.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>73.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25070,28 +25070,28 @@
         <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>134.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>282.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>184.1611964156229</v>
+        <v>90.6811537166335</v>
       </c>
       <c r="P34" t="n">
         <v>398.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>436.839266425598</v>
       </c>
       <c r="R34" t="n">
         <v>437.6021279811511</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>73.37347970285543</v>
       </c>
       <c r="T34" t="n">
         <v>0</v>
@@ -25313,22 +25313,22 @@
         <v>231.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>282.1850752716849</v>
       </c>
       <c r="O37" t="n">
         <v>351.445564079015</v>
       </c>
       <c r="P37" t="n">
-        <v>398.4478973282775</v>
+        <v>363.7605665406311</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>320.871224186894</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>73.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25544,28 +25544,28 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>134.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>231.6316114025499</v>
+        <v>211.0569666687515</v>
       </c>
       <c r="N40" t="n">
-        <v>282.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>351.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>278.366864194048</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
         <v>436.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>437.6021279811511</v>
       </c>
       <c r="S40" t="n">
-        <v>73.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
         <v>0</v>
@@ -25596,13 +25596,13 @@
         <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>271.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>226.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
@@ -25641,16 +25641,16 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>61.37964629535452</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>29.15682326199851</v>
+        <v>408.6755817285639</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>471.2212965486107</v>
       </c>
       <c r="V41" t="n">
         <v>451.8510241668239</v>
@@ -25659,7 +25659,7 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>414.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25672,7 +25672,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>206.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C42" t="n">
         <v>0</v>
@@ -25681,13 +25681,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>164.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>0</v>
+        <v>102.3830262446605</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -25720,22 +25720,22 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>369.2737972923793</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>288.5639999646113</v>
       </c>
       <c r="T42" t="n">
-        <v>227.3577652175138</v>
+        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>236.5106671915202</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>223.1322955101433</v>
+        <v>254.3731429098285</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25751,7 +25751,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>109.1138003370787</v>
       </c>
       <c r="C43" t="n">
         <v>94.72524664804467</v>
@@ -25805,7 +25805,7 @@
         <v>184.3734797028554</v>
       </c>
       <c r="T43" t="n">
-        <v>32.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -25833,16 +25833,16 @@
         <v>418.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>386.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>347.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>177.2558834167835</v>
       </c>
       <c r="F44" t="n">
-        <v>341.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
         <v>340.7573722870162</v>
@@ -25851,7 +25851,7 @@
         <v>345.0096587035274</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>87.08115968268461</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -25878,13 +25878,13 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>187.8785988282945</v>
       </c>
       <c r="S44" t="n">
         <v>431.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>523.6755817285639</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -25893,10 +25893,10 @@
         <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>293.6186592256001</v>
+        <v>575.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>529.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -25918,19 +25918,19 @@
         <v>284.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>279.6720972219126</v>
       </c>
       <c r="F45" t="n">
         <v>276.6362423378769</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>262.7395358750273</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>269.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>154.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,7 +25954,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>110.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>484.2737972923793</v>
@@ -25966,19 +25966,19 @@
         <v>342.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>300.1159711123823</v>
+        <v>337.2103597601867</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>351.5106671915202</v>
       </c>
       <c r="W45" t="n">
         <v>369.3731429098285</v>
       </c>
       <c r="X45" t="n">
-        <v>356.8627394453875</v>
+        <v>78.83156371699124</v>
       </c>
       <c r="Y45" t="n">
-        <v>336.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4162705.540051035</v>
+        <v>4162705.540051036</v>
       </c>
     </row>
     <row r="6">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8180383.038476371</v>
+        <v>8180383.038476375</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9097175.004882477</v>
+        <v>9097175.004882479</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10107933.92052089</v>
+        <v>10107933.9205209</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11118468.48907722</v>
+        <v>11118468.48907723</v>
       </c>
     </row>
     <row r="13">
@@ -26296,7 +26296,7 @@
         <v>1031575.830543489</v>
       </c>
       <c r="K2" t="n">
-        <v>1133023.607169219</v>
+        <v>1133023.60716922</v>
       </c>
       <c r="L2" t="n">
         <v>1133023.60716922</v>
@@ -26305,13 +26305,13 @@
         <v>1133023.60716922</v>
       </c>
       <c r="N2" t="n">
-        <v>1133023.60716922</v>
+        <v>1133023.607169219</v>
       </c>
       <c r="O2" t="n">
-        <v>910365.7471128515</v>
+        <v>910365.7471128514</v>
       </c>
       <c r="P2" t="n">
-        <v>612776.2557999014</v>
+        <v>612776.2557999016</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>553894.4209411234</v>
+        <v>549073.4019700913</v>
       </c>
       <c r="C4" t="n">
-        <v>552148.6767468527</v>
+        <v>547327.6577758205</v>
       </c>
       <c r="D4" t="n">
-        <v>550400.5643416208</v>
+        <v>545579.5453705885</v>
       </c>
       <c r="E4" t="n">
-        <v>475508.5085360265</v>
+        <v>470687.4895649943</v>
       </c>
       <c r="F4" t="n">
-        <v>523396.3864423811</v>
+        <v>518575.367471349</v>
       </c>
       <c r="G4" t="n">
-        <v>521737.444927747</v>
+        <v>516916.4259567147</v>
       </c>
       <c r="H4" t="n">
-        <v>520076.2008969562</v>
+        <v>515255.1819259241</v>
       </c>
       <c r="I4" t="n">
-        <v>518412.637742535</v>
+        <v>513591.6187715029</v>
       </c>
       <c r="J4" t="n">
-        <v>464813.3679854201</v>
+        <v>460130.3405348168</v>
       </c>
       <c r="K4" t="n">
-        <v>523864.6016459742</v>
+        <v>519172.084144613</v>
       </c>
       <c r="L4" t="n">
-        <v>522143.8849986775</v>
+        <v>517451.3674973165</v>
       </c>
       <c r="M4" t="n">
-        <v>520420.7089809946</v>
+        <v>515728.1914796335</v>
       </c>
       <c r="N4" t="n">
-        <v>518695.0553227372</v>
+        <v>514002.5378213761</v>
       </c>
       <c r="O4" t="n">
-        <v>386080.5898356722</v>
+        <v>381397.5623850689</v>
       </c>
       <c r="P4" t="n">
-        <v>210633.5645263094</v>
+        <v>205950.5370757062</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>236841.7413665268</v>
+        <v>241662.7603375589</v>
       </c>
       <c r="C6" t="n">
-        <v>528987.4855607973</v>
+        <v>533808.5045318297</v>
       </c>
       <c r="D6" t="n">
-        <v>530735.5979660292</v>
+        <v>535556.6169370614</v>
       </c>
       <c r="E6" t="n">
-        <v>320135.988991463</v>
+        <v>324957.0079624951</v>
       </c>
       <c r="F6" t="n">
-        <v>488607.7471465422</v>
+        <v>493428.7661175742</v>
       </c>
       <c r="G6" t="n">
-        <v>531066.6886611761</v>
+        <v>535887.7076322087</v>
       </c>
       <c r="H6" t="n">
-        <v>532727.9326919671</v>
+        <v>537548.9516629986</v>
       </c>
       <c r="I6" t="n">
-        <v>534391.4958463882</v>
+        <v>539212.5148174197</v>
       </c>
       <c r="J6" t="n">
-        <v>87075.73755806932</v>
+        <v>91758.76500867234</v>
       </c>
       <c r="K6" t="n">
-        <v>445499.8645232451</v>
+        <v>450192.3820246067</v>
       </c>
       <c r="L6" t="n">
-        <v>539220.5811705419</v>
+        <v>543913.0986719029</v>
       </c>
       <c r="M6" t="n">
-        <v>540943.7571882254</v>
+        <v>545636.2746895859</v>
       </c>
       <c r="N6" t="n">
-        <v>542669.4108464823</v>
+        <v>547361.9283478432</v>
       </c>
       <c r="O6" t="n">
-        <v>411557.6752771793</v>
+        <v>416240.7027277824</v>
       </c>
       <c r="P6" t="n">
-        <v>349483.144273592</v>
+        <v>354166.1717241954</v>
       </c>
     </row>
   </sheetData>
@@ -26990,10 +26990,10 @@
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>174</v>
@@ -27002,10 +27002,10 @@
         <v>115</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
         <v>-0</v>
@@ -27445,7 +27445,7 @@
         <v>400</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -27484,10 +27484,10 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>400</v>
+        <v>264.7015671255647</v>
       </c>
       <c r="T2" t="n">
-        <v>264.7015671255645</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>264.6481137848265</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27557,10 +27557,10 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>143.9573181542525</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27606,16 +27606,16 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>400</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H4" t="n">
         <v>400</v>
       </c>
       <c r="I4" t="n">
+        <v>176.6334556201183</v>
+      </c>
+      <c r="J4" t="n">
         <v>400</v>
-      </c>
-      <c r="J4" t="n">
-        <v>299.9897043938366</v>
       </c>
       <c r="K4" t="n">
         <v>288.520773801143</v>
@@ -27645,13 +27645,13 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>287.5072526546621</v>
       </c>
       <c r="U4" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
         <v>226.3728098387097</v>
@@ -27679,17 +27679,17 @@
         <v>400</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
         <v>400</v>
       </c>
-      <c r="H5" t="n">
-        <v>264.7015671255642</v>
-      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -27721,10 +27721,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>264.7015671255645</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27761,10 +27761,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27794,16 +27794,16 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>400</v>
+        <v>380.7294189199613</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27812,10 +27812,10 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>342.2743756165773</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27837,13 +27837,13 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>373.8591682926692</v>
       </c>
       <c r="F7" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G7" t="n">
-        <v>283.2613305956835</v>
+        <v>245.04387284153</v>
       </c>
       <c r="H7" t="n">
         <v>228.7711261016186</v>
@@ -27882,7 +27882,7 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27907,7 +27907,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>264.7015671255648</v>
+        <v>400</v>
       </c>
       <c r="C8" t="n">
         <v>400</v>
@@ -27928,7 +27928,7 @@
         <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>13.82296829727056</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,25 +27955,25 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
       </c>
       <c r="V8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>400</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="Y8" t="n">
         <v>400</v>
@@ -27989,19 +27989,19 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>303.3742880620966</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>158.62369561122</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>332.1680871864211</v>
@@ -28043,13 +28043,13 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="X9" t="n">
         <v>400</v>
@@ -28065,10 +28065,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>400</v>
       </c>
       <c r="C10" t="n">
-        <v>272.7252466480447</v>
+        <v>400</v>
       </c>
       <c r="D10" t="n">
         <v>400</v>
@@ -28089,7 +28089,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J10" t="n">
-        <v>351.4338015463763</v>
+        <v>180.8244607100833</v>
       </c>
       <c r="K10" t="n">
         <v>288.520773801143</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
+        <v>362.3734797028554</v>
+      </c>
+      <c r="T10" t="n">
         <v>400</v>
-      </c>
-      <c r="T10" t="n">
-        <v>210.0245665062577</v>
       </c>
       <c r="U10" t="n">
         <v>150.9583912744579</v>
       </c>
       <c r="V10" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W10" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X10" t="n">
         <v>400</v>
-      </c>
-      <c r="W10" t="n">
-        <v>400</v>
-      </c>
-      <c r="X10" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28244,7 +28244,7 @@
         <v>225</v>
       </c>
       <c r="I12" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J12" t="n">
         <v>225</v>
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>26.99048536749052</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>19.11687125883908</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28402,7 +28402,7 @@
         <v>276</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>149.8229682972704</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28435,7 +28435,7 @@
         <v>276</v>
       </c>
       <c r="T14" t="n">
-        <v>275.7418086145853</v>
+        <v>276</v>
       </c>
       <c r="U14" t="n">
         <v>276</v>
@@ -28490,19 +28490,19 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>276</v>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>269.4578866530732</v>
-      </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>269.4578866530731</v>
       </c>
       <c r="Q15" t="n">
         <v>276</v>
@@ -28639,7 +28639,7 @@
         <v>276</v>
       </c>
       <c r="I17" t="n">
-        <v>149.8229682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28675,7 +28675,7 @@
         <v>276</v>
       </c>
       <c r="U17" t="n">
-        <v>276</v>
+        <v>275.7418086145852</v>
       </c>
       <c r="V17" t="n">
         <v>276</v>
@@ -28718,7 +28718,7 @@
         <v>276</v>
       </c>
       <c r="I18" t="n">
-        <v>217.1263858913485</v>
+        <v>276</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28727,13 +28727,13 @@
         <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>96.37862156259342</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="N18" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>276</v>
@@ -28742,7 +28742,7 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>173.0792650904796</v>
+        <v>210.5842725444217</v>
       </c>
       <c r="R18" t="n">
         <v>276</v>
@@ -28876,7 +28876,7 @@
         <v>276</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>149.8229682972704</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>250.6204074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
         <v>276</v>
@@ -28967,19 +28967,19 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>37.505007453942</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>210.5842725444217</v>
       </c>
       <c r="P21" t="n">
         <v>276</v>
       </c>
       <c r="Q21" t="n">
-        <v>173.0792650904796</v>
+        <v>276</v>
       </c>
       <c r="R21" t="n">
         <v>276</v>
@@ -29098,7 +29098,7 @@
         <v>276</v>
       </c>
       <c r="D23" t="n">
-        <v>276</v>
+        <v>275.7418086145858</v>
       </c>
       <c r="E23" t="n">
         <v>276</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.6204074428798</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
         <v>276</v>
@@ -29192,7 +29192,7 @@
         <v>276</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>276</v>
       </c>
       <c r="J24" t="n">
         <v>276</v>
@@ -29204,7 +29204,7 @@
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>96.37862156259382</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
         <v>0</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>210.5842725444217</v>
       </c>
       <c r="R24" t="n">
         <v>276</v>
@@ -29435,7 +29435,7 @@
         <v>225</v>
       </c>
       <c r="K27" t="n">
-        <v>19.11687125883918</v>
+        <v>225</v>
       </c>
       <c r="L27" t="n">
         <v>225</v>
@@ -29444,7 +29444,7 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
@@ -29669,28 +29669,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>44.4985967846923</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>289</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="n">
-        <v>160.4193316942132</v>
-      </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
       <c r="Q30" t="n">
-        <v>173.0792650904796</v>
+        <v>289</v>
       </c>
       <c r="R30" t="n">
         <v>289</v>
@@ -29824,7 +29824,7 @@
         <v>289</v>
       </c>
       <c r="I32" t="n">
-        <v>146.3397682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29860,7 +29860,7 @@
         <v>289</v>
       </c>
       <c r="U32" t="n">
-        <v>289</v>
+        <v>285.2586086145854</v>
       </c>
       <c r="V32" t="n">
         <v>289</v>
@@ -29903,16 +29903,16 @@
         <v>289</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>289</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>261.6249826760411</v>
       </c>
       <c r="L33" t="n">
-        <v>160.4193316942129</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -29924,10 +29924,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>289</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>289</v>
@@ -30140,13 +30140,13 @@
         <v>289</v>
       </c>
       <c r="I36" t="n">
-        <v>217.1263858913485</v>
+        <v>289</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>160.4193316942129</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -30155,16 +30155,16 @@
         <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>261.6249826760409</v>
       </c>
       <c r="R36" t="n">
         <v>289</v>
@@ -30289,7 +30289,7 @@
         <v>289</v>
       </c>
       <c r="F38" t="n">
-        <v>289</v>
+        <v>285.2586086145857</v>
       </c>
       <c r="G38" t="n">
         <v>289</v>
@@ -30343,7 +30343,7 @@
         <v>289</v>
       </c>
       <c r="X38" t="n">
-        <v>285.2586086145856</v>
+        <v>289</v>
       </c>
       <c r="Y38" t="n">
         <v>289</v>
@@ -30386,22 +30386,22 @@
         <v>0</v>
       </c>
       <c r="L39" t="n">
+        <v>261.624982676041</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
         <v>289</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
-      <c r="P39" t="n">
-        <v>88.54571758556126</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>289</v>
@@ -30623,13 +30623,13 @@
         <v>178</v>
       </c>
       <c r="L42" t="n">
+        <v>40.11050739434445</v>
+      </c>
+      <c r="M42" t="n">
         <v>178</v>
       </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
       <c r="N42" t="n">
-        <v>173.5891163363538</v>
+        <v>178</v>
       </c>
       <c r="O42" t="n">
         <v>178</v>
@@ -30693,10 +30693,10 @@
         <v>178</v>
       </c>
       <c r="I43" t="n">
-        <v>178</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J43" t="n">
-        <v>118.1900481915376</v>
+        <v>67.94374376117838</v>
       </c>
       <c r="K43" t="n">
         <v>178</v>
@@ -30729,7 +30729,7 @@
         <v>178</v>
       </c>
       <c r="U43" t="n">
-        <v>178</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V43" t="n">
         <v>178</v>
@@ -30854,10 +30854,10 @@
         <v>63</v>
       </c>
       <c r="J45" t="n">
-        <v>63</v>
+        <v>46.60248179099561</v>
       </c>
       <c r="K45" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
         <v>63</v>
@@ -30866,13 +30866,13 @@
         <v>63</v>
       </c>
       <c r="N45" t="n">
-        <v>46.60248179099561</v>
+        <v>63</v>
       </c>
       <c r="O45" t="n">
         <v>63</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="Q45" t="n">
         <v>63</v>
@@ -34746,13 +34746,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K2" t="n">
-        <v>158.9610829645592</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>267.08596544146</v>
       </c>
       <c r="N2" t="n">
         <v>619.4144644189528</v>
@@ -34761,7 +34761,7 @@
         <v>825</v>
       </c>
       <c r="P2" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>443.0293889420883</v>
@@ -34892,16 +34892,16 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>154.95612715847</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>264.7207555579288</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -34931,13 +34931,13 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>77.48268614840443</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -34983,25 +34983,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230993</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>194.106436475533</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N5" t="n">
-        <v>619.4144644189528</v>
+        <v>262.3666294754967</v>
       </c>
       <c r="O5" t="n">
         <v>825</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35123,13 +35123,13 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>92.8782634557126</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>38.21745775415347</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -35168,7 +35168,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35217,13 +35217,13 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K8" t="n">
-        <v>481.2432843396987</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L8" t="n">
-        <v>825</v>
+        <v>576.0770475334448</v>
       </c>
       <c r="M8" t="n">
         <v>516.0089179080152</v>
@@ -35232,13 +35232,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O8" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,10 +35351,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>112.8861996629213</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
         <v>114.4637819444445</v>
@@ -35375,7 +35375,7 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>316.1648527104684</v>
+        <v>145.5555118741756</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35457,19 +35457,19 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230993</v>
+        <v>262.3666294754967</v>
       </c>
       <c r="L11" t="n">
         <v>825</v>
       </c>
       <c r="M11" t="n">
-        <v>267.08596544146</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35530,7 +35530,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J12" t="n">
         <v>350.2086062376757</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>301.0818607161775</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>132.7828757734923</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35697,13 +35697,13 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>825</v>
+        <v>467.9521650565442</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N14" t="n">
-        <v>262.3666294754967</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
         <v>825</v>
@@ -35776,7 +35776,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>550.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
         <v>86.95004216450428</v>
@@ -35785,10 +35785,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>510.9149085558196</v>
+        <v>517.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>113.6660045146532</v>
+        <v>383.1238911677262</v>
       </c>
       <c r="Q15" t="n">
         <v>102.9207349095204</v>
@@ -35928,13 +35928,13 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>481.2432843396987</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,13 +35943,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>467.9521650565441</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>825</v>
       </c>
       <c r="Q17" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,7 +36004,7 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>58.87361410865147</v>
       </c>
       <c r="J18" t="n">
         <v>125.2086062376757</v>
@@ -36013,13 +36013,13 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>370.4699969112804</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>86.95004216450428</v>
+        <v>362.9500421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>410.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
         <v>517.4570219027464</v>
@@ -36028,7 +36028,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>37.50500745394206</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36168,7 +36168,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>262.366629475489</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -36177,13 +36177,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N20" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>467.9521650565441</v>
+        <v>825.0000000000039</v>
       </c>
       <c r="P20" t="n">
-        <v>825</v>
+        <v>825.0000000000039</v>
       </c>
       <c r="Q20" t="n">
         <v>443.0293889420883</v>
@@ -36253,19 +36253,19 @@
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>124.4550496184463</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N21" t="n">
-        <v>410.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>452.0412944471681</v>
       </c>
       <c r="P21" t="n">
         <v>389.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>102.9207349095204</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36411,19 +36411,19 @@
         <v>825</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>61.50042986040868</v>
       </c>
       <c r="N23" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>825.0000000000039</v>
       </c>
       <c r="Q23" t="n">
-        <v>194.1064364755331</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,7 +36478,7 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>58.87361410865147</v>
       </c>
       <c r="J24" t="n">
         <v>401.2086062376757</v>
@@ -36490,7 +36490,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>183.3286637270981</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
         <v>134.6265501086548</v>
@@ -36502,7 +36502,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>37.50500745394206</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,25 +36642,25 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>779</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>779.0000000000139</v>
+        <v>779.0000000000107</v>
       </c>
       <c r="P26" t="n">
-        <v>464.0813991641975</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>293.6412170941275</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36721,7 +36721,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
-        <v>210.2207258996305</v>
+        <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
         <v>499.091375348687</v>
@@ -36730,7 +36730,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>359.6265501086548</v>
+        <v>153.743421367494</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
@@ -36879,22 +36879,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>184.7515739098073</v>
+        <v>779.0000000000002</v>
       </c>
       <c r="L29" t="n">
-        <v>616.9388964877596</v>
+        <v>779</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>22.6904703976295</v>
       </c>
       <c r="O29" t="n">
-        <v>779.0000000000198</v>
+        <v>779.0000000000157</v>
       </c>
       <c r="P29" t="n">
-        <v>779.0000000000198</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36955,7 +36955,7 @@
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>414.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K30" t="n">
         <v>191.1038546407913</v>
@@ -36967,16 +36967,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N30" t="n">
-        <v>295.0458818028679</v>
+        <v>179.1251468933471</v>
       </c>
       <c r="O30" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>113.6660045146532</v>
+        <v>402.6660045146532</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>115.9207349095204</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37113,25 +37113,25 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>314.5466542276387</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>779</v>
+        <v>182.2760059786387</v>
       </c>
       <c r="L32" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>779.0000000000243</v>
+        <v>779.0000000000189</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>779.0000000000189</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37189,16 +37189,16 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>71.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K33" t="n">
-        <v>191.1038546407913</v>
+        <v>452.7288373168324</v>
       </c>
       <c r="L33" t="n">
-        <v>434.5107070428999</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
         <v>86.95004216450428</v>
@@ -37210,10 +37210,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>402.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>115.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37350,28 +37350,28 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
         <v>779</v>
       </c>
       <c r="L35" t="n">
-        <v>554.8140140109142</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>698.2849238865825</v>
       </c>
       <c r="N35" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O35" t="n">
-        <v>779.0000000000407</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>465.7531112509096</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37426,13 +37426,13 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>71.87361410865147</v>
       </c>
       <c r="J36" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K36" t="n">
-        <v>351.5231863350043</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L36" t="n">
         <v>274.091375348687</v>
@@ -37441,16 +37441,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
-        <v>134.6265501086548</v>
+        <v>423.6265501086548</v>
       </c>
       <c r="O36" t="n">
         <v>241.4570219027464</v>
       </c>
       <c r="P36" t="n">
-        <v>402.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>88.54571758556126</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>241.5671252618083</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K38" t="n">
-        <v>779</v>
+        <v>716.8751175230996</v>
       </c>
       <c r="L38" t="n">
-        <v>779</v>
+        <v>616.9388964877652</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
@@ -37602,10 +37602,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O38" t="n">
-        <v>779.000000000058</v>
+        <v>70.49138090983999</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>779.0000000000434</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -37672,7 +37672,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>563.0913753486871</v>
+        <v>535.716358024728</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
@@ -37684,10 +37684,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P39" t="n">
-        <v>202.2117221002144</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>115.9207349095204</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>10.19736373309691</v>
       </c>
       <c r="K41" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L41" t="n">
-        <v>778.9999999999999</v>
+        <v>779</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>779.0000000000962</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>366.6207460599685</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37909,13 +37909,13 @@
         <v>369.1038546407913</v>
       </c>
       <c r="L42" t="n">
-        <v>452.091375348687</v>
+        <v>314.2018827430314</v>
       </c>
       <c r="M42" t="n">
-        <v>86.95004216450428</v>
+        <v>264.9500421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>308.2156664450087</v>
+        <v>312.6265501086548</v>
       </c>
       <c r="O42" t="n">
         <v>419.4570219027464</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>1.366544379881727</v>
+        <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>82.92109935562986</v>
+        <v>32.67479492527061</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>27.04160872554206</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38064,22 +38064,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>688.2341332419844</v>
       </c>
       <c r="L44" t="n">
         <v>779</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>779.0000000001135</v>
       </c>
       <c r="P44" t="n">
-        <v>331.8107509151303</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38140,10 +38140,10 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>188.2086062376757</v>
+        <v>171.8110880286713</v>
       </c>
       <c r="K45" t="n">
-        <v>254.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L45" t="n">
         <v>337.091375348687</v>
@@ -38152,13 +38152,13 @@
         <v>149.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>181.2290318996504</v>
+        <v>197.6265501086548</v>
       </c>
       <c r="O45" t="n">
         <v>304.4570219027464</v>
       </c>
       <c r="P45" t="n">
-        <v>113.6660045146532</v>
+        <v>176.6660045146532</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
